--- a/results/542_z18/5_quantification/542_z18_quantification.xlsx
+++ b/results/542_z18/5_quantification/542_z18_quantification.xlsx
@@ -10,8 +10,9 @@
     <sheet name="per_image" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="field" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="width" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="per_lacuna" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="notes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="biological_limits" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="per_lacuna" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="notes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,11 +447,6 @@
           <t>interior_lacuna_count</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>n_bridges</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -472,9 +468,6 @@
       <c r="E2" t="n">
         <v>11</v>
       </c>
-      <c r="F2" t="n">
-        <v>14</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -712,7 +705,7 @@
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>4.0023</v>
+        <v>3.7441</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -735,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>357.0909</v>
+        <v>371.6364</v>
       </c>
       <c r="D13" t="n">
-        <v>376</v>
+        <v>348</v>
       </c>
       <c r="E13" t="n">
-        <v>125.5041</v>
+        <v>149.3474</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -764,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>968.7273</v>
+        <v>978.9091</v>
       </c>
       <c r="D14" t="n">
-        <v>1007</v>
+        <v>929</v>
       </c>
       <c r="E14" t="n">
-        <v>301.7307</v>
+        <v>338.093</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -793,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>972.6153</v>
+        <v>2009.921</v>
       </c>
       <c r="D15" t="n">
-        <v>961.4773</v>
+        <v>1584.5088</v>
       </c>
       <c r="E15" t="n">
-        <v>477.4357</v>
+        <v>1063.1721</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -822,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="E16" t="n">
-        <v>17.2743</v>
+        <v>56.4624</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -851,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>30.7951</v>
+        <v>24.271</v>
       </c>
       <c r="D17" t="n">
-        <v>31.5344</v>
+        <v>23.3016</v>
       </c>
       <c r="E17" t="n">
-        <v>5.1473</v>
+        <v>4.1168</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1025,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02900112</v>
+        <v>0.03007332</v>
       </c>
       <c r="D23" t="n">
-        <v>0.02856139</v>
+        <v>0.02907357</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00576019</v>
+        <v>0.00746476</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1054,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.03326266</v>
+        <v>0.03369617</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03409786</v>
+        <v>0.0345758</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0063714</v>
+        <v>0.00810109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1083,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.3636</v>
+        <v>2.4334</v>
       </c>
       <c r="D25" t="n">
-        <v>2.2772</v>
+        <v>2.3689</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4767</v>
+        <v>0.6696</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1112,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>239.9091</v>
+        <v>286.7273</v>
       </c>
       <c r="D26" t="n">
-        <v>231</v>
+        <v>312</v>
       </c>
       <c r="E26" t="n">
-        <v>115.7544</v>
+        <v>153.7186</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1141,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>479.8182</v>
+        <v>664.3636</v>
       </c>
       <c r="D27" t="n">
-        <v>438</v>
+        <v>557</v>
       </c>
       <c r="E27" t="n">
-        <v>237.4463</v>
+        <v>363.4653</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1170,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>397.1731</v>
+        <v>414.3253</v>
       </c>
       <c r="D28" t="n">
-        <v>421.5635</v>
+        <v>398.7767</v>
       </c>
       <c r="E28" t="n">
-        <v>144.9593</v>
+        <v>171.8057</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1199,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1090.3199</v>
+        <v>1105.4692</v>
       </c>
       <c r="D29" t="n">
-        <v>1145.6438</v>
+        <v>1032.2813</v>
       </c>
       <c r="E29" t="n">
-        <v>345.1069</v>
+        <v>386.0866</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1228,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9.3636</v>
+        <v>9.0909</v>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>4.6534</v>
+        <v>5.0091</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1257,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13.2727</v>
+        <v>13</v>
       </c>
       <c r="D31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>4.7559</v>
+        <v>5.0794</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1286,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>14.8182</v>
+        <v>15</v>
       </c>
       <c r="D32" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E32" t="n">
-        <v>5.115</v>
+        <v>5.2536</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1315,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5.5062</v>
+        <v>6.5261</v>
       </c>
       <c r="D33" t="n">
-        <v>5.5614</v>
+        <v>6.5998</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5316</v>
+        <v>0.6532</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1400,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>34325</v>
+        <v>34260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1420,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03407276</v>
+        <v>0.03400824</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1440,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>395</v>
+        <v>701</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1460,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0003921</v>
+        <v>0.00069585</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1520,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>663</v>
+        <v>277</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>51.7722</v>
+        <v>123.6823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1580,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03838905</v>
+        <v>0.03846082</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1600,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03399229</v>
+        <v>0.0338477</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1673,7 +1666,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6.1251</v>
+        <v>7.3706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1693,7 +1686,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1733,7 +1726,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1753,7 +1746,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32892</v>
+        <v>32773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1772,1386 +1765,407 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG13"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>lacuna_id</t>
+          <t>block</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>area_px2</t>
+          <t>item</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>major_axis_length_px</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>minor_axis_length_px</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>aspect_ratio</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>eccentricity</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>solidity</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>orientation_rad</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>centroid_row_px</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>centroid_col_px</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>on_border</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>roots_count</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ring_length_r30_px</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ring_length_r60_px</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>owned_length_px</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>edge_count</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>mean_edge_length_px</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>perimeter_px</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>ring_area_r30_px2</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>ring_area_r60_px2</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>in_frame_fraction_r30</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>in_frame_fraction_r60</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>ring_density_r30</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>ring_density_r60</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>roots_per_100px_perimeter</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>ring_attached_length_r30_px</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>ring_attached_length_r60_px</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>ring_length_w_r30_px</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>ring_length_w_r60_px</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>sholl_crossings_r10</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>sholl_crossings_r20</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>sholl_crossings_r30</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>ring_width_mean_r30_px</t>
+          <t>value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>report only, nothing is pruned or filtered by this block</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>validated</t>
+        </is>
+      </c>
+      <c r="C3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>along the network from the owning lacuna's surface to a thread end</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>range_um</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[25.0, 50.0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>range_px_applied</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[192, 385]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>range_um_applied</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[24.96, 50.05]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>n_threads</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>median_um</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>20.6909</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>p10_um</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>p90_um</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>40.0725</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>max_um</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50.0433</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fraction_in_range</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.3547</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>fraction_below_range</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6453</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>fraction_above_range</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>threads leaving the lacuna surface, interior lacunae only</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>n_lacunae</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2 x the distance transform of the mask at each sampled skeleton pixel</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>is_an_upper_bound</t>
+        </is>
+      </c>
+      <c r="C22" t="b">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
-        <v>602</v>
-      </c>
-      <c r="C2" t="n">
-        <v>56.2113</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.2037</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2.651</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.9261</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.6645</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-0.3574</v>
-      </c>
-      <c r="I2" t="n">
-        <v>16.2608</v>
-      </c>
-      <c r="J2" t="n">
-        <v>914.0415</v>
-      </c>
-      <c r="K2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M2" t="n">
-        <v>196</v>
-      </c>
-      <c r="N2" t="n">
-        <v>529</v>
-      </c>
-      <c r="O2" t="n">
-        <v>586.6884</v>
-      </c>
-      <c r="P2" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>22.5649</v>
-      </c>
-      <c r="R2" t="n">
-        <v>142.8112</v>
-      </c>
-      <c r="S2" t="n">
-        <v>4575</v>
-      </c>
-      <c r="T2" t="n">
-        <v>11641</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.673</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.6207</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.04284153</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.04544283</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.8009</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>188</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>296</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>223.5807</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>596.1442</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>5.2001</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>5924</v>
-      </c>
-      <c r="C3" t="n">
-        <v>181.0427</v>
-      </c>
-      <c r="D3" t="n">
-        <v>48.2611</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3.7513</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.9638</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-0.0924</v>
-      </c>
-      <c r="I3" t="n">
-        <v>129.8709</v>
-      </c>
-      <c r="J3" t="n">
-        <v>638.6273</v>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>19</v>
-      </c>
-      <c r="M3" t="n">
-        <v>574</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1322</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1962.1139</v>
-      </c>
-      <c r="P3" t="n">
-        <v>73</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>26.8783</v>
-      </c>
-      <c r="R3" t="n">
-        <v>625.725</v>
-      </c>
-      <c r="S3" t="n">
-        <v>16860</v>
-      </c>
-      <c r="T3" t="n">
-        <v>35430</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.9542</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.8861</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.03404508</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.03731301</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>3.0365</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>523</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>936</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>647.8843000000001</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1481.8519</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>6.4381</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>4438</v>
-      </c>
-      <c r="C4" t="n">
-        <v>160.6807</v>
-      </c>
-      <c r="D4" t="n">
-        <v>35.4482</v>
-      </c>
-      <c r="E4" t="n">
-        <v>4.5328</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9754</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.8989</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-0.2181</v>
-      </c>
-      <c r="I4" t="n">
-        <v>173.3515</v>
-      </c>
-      <c r="J4" t="n">
-        <v>382.514</v>
-      </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M4" t="n">
-        <v>385</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1044</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1073.3646</v>
-      </c>
-      <c r="P4" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>32.5262</v>
-      </c>
-      <c r="R4" t="n">
-        <v>377.0193</v>
-      </c>
-      <c r="S4" t="n">
-        <v>13152</v>
-      </c>
-      <c r="T4" t="n">
-        <v>31926</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.02927311</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.03270062</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.1219</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>231</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>570</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>421.5635</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1170.7321</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>5.8326</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4342</v>
-      </c>
-      <c r="C5" t="n">
-        <v>127.7957</v>
-      </c>
-      <c r="D5" t="n">
-        <v>43.8553</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2.914</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9393</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.893</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-0.1983</v>
-      </c>
-      <c r="I5" t="n">
-        <v>210.2996</v>
-      </c>
-      <c r="J5" t="n">
-        <v>874.1078</v>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>7</v>
-      </c>
-      <c r="M5" t="n">
-        <v>431</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1139</v>
-      </c>
-      <c r="O5" t="n">
-        <v>961.4773</v>
-      </c>
-      <c r="P5" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>41.8034</v>
-      </c>
-      <c r="R5" t="n">
-        <v>337.7056</v>
-      </c>
-      <c r="S5" t="n">
-        <v>12118</v>
-      </c>
-      <c r="T5" t="n">
-        <v>29514</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.03556693</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.03859185</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.0728</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>222</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>378</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>481.0904</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1305.6266</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>5.2892</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>5254</v>
-      </c>
-      <c r="C6" t="n">
-        <v>148.6874</v>
-      </c>
-      <c r="D6" t="n">
-        <v>46.2758</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3.2131</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.9503</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.9227</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-0.0688</v>
-      </c>
-      <c r="I6" t="n">
-        <v>369.2524</v>
-      </c>
-      <c r="J6" t="n">
-        <v>79.7008</v>
-      </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>6</v>
-      </c>
-      <c r="M6" t="n">
-        <v>329</v>
-      </c>
-      <c r="N6" t="n">
-        <v>924</v>
-      </c>
-      <c r="O6" t="n">
-        <v>290.3503</v>
-      </c>
-      <c r="P6" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>24.1959</v>
-      </c>
-      <c r="R6" t="n">
-        <v>371.8061</v>
-      </c>
-      <c r="S6" t="n">
-        <v>13199</v>
-      </c>
-      <c r="T6" t="n">
-        <v>31872</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.9956</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.02492613</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.02899096</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.6137</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>170</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>228</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>367.5341</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1041.2052</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>6.086</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3405</v>
-      </c>
-      <c r="C7" t="n">
-        <v>124.6016</v>
-      </c>
-      <c r="D7" t="n">
-        <v>35.4524</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3.5146</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.9587</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.8958</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-0.0028</v>
-      </c>
-      <c r="I7" t="n">
-        <v>532.2396</v>
-      </c>
-      <c r="J7" t="n">
-        <v>401.3151</v>
-      </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>10</v>
-      </c>
-      <c r="M7" t="n">
-        <v>325</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1007</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1513.6509</v>
-      </c>
-      <c r="P7" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>31.5344</v>
-      </c>
-      <c r="R7" t="n">
-        <v>308.5929</v>
-      </c>
-      <c r="S7" t="n">
-        <v>11379</v>
-      </c>
-      <c r="T7" t="n">
-        <v>28385</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.02856139</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.03547648</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>3.2405</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>254</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>630</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>361.0488</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1145.6438</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>5.5614</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4133</v>
-      </c>
-      <c r="C8" t="n">
-        <v>149.9613</v>
-      </c>
-      <c r="D8" t="n">
-        <v>37.557</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3.9929</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.9681</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.861</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.1428</v>
-      </c>
-      <c r="I8" t="n">
-        <v>589.0707</v>
-      </c>
-      <c r="J8" t="n">
-        <v>924.0489</v>
-      </c>
-      <c r="K8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>8</v>
-      </c>
-      <c r="M8" t="n">
-        <v>473</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1313</v>
-      </c>
-      <c r="O8" t="n">
-        <v>928.9503999999999</v>
-      </c>
-      <c r="P8" t="n">
-        <v>37</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>25.1068</v>
-      </c>
-      <c r="R8" t="n">
-        <v>382.8772</v>
-      </c>
-      <c r="S8" t="n">
-        <v>12760</v>
-      </c>
-      <c r="T8" t="n">
-        <v>30245</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.03706897</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.04341213</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.0894</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>302</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>649</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>537.73</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1477.3961</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>5.7038</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2572</v>
-      </c>
-      <c r="C9" t="n">
-        <v>119.2938</v>
-      </c>
-      <c r="D9" t="n">
-        <v>30.2433</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3.9445</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.9673</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.8307</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.0493</v>
-      </c>
-      <c r="I9" t="n">
-        <v>570.0315000000001</v>
-      </c>
-      <c r="J9" t="n">
-        <v>785.133</v>
-      </c>
-      <c r="K9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>7</v>
-      </c>
-      <c r="M9" t="n">
-        <v>302</v>
-      </c>
-      <c r="N9" t="n">
-        <v>892</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1068.1514</v>
-      </c>
-      <c r="P9" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>32.3682</v>
-      </c>
-      <c r="R9" t="n">
-        <v>306.4924</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10697</v>
-      </c>
-      <c r="T9" t="n">
-        <v>26160</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.02823221</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.03409786</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.2839</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>192</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>438</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>319.4092</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>987.4529</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>5.311</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="n">
-        <v>3684</v>
-      </c>
-      <c r="C10" t="n">
-        <v>159.3366</v>
-      </c>
-      <c r="D10" t="n">
-        <v>32.9692</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4.8329</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.9784</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.8054</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.098</v>
-      </c>
-      <c r="I10" t="n">
-        <v>739.4517</v>
-      </c>
-      <c r="J10" t="n">
-        <v>247.5361</v>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>9</v>
-      </c>
-      <c r="M10" t="n">
-        <v>376</v>
-      </c>
-      <c r="N10" t="n">
-        <v>978</v>
-      </c>
-      <c r="O10" t="n">
-        <v>457.3036</v>
-      </c>
-      <c r="P10" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>26.9002</v>
-      </c>
-      <c r="R10" t="n">
-        <v>437.262</v>
-      </c>
-      <c r="S10" t="n">
-        <v>14880</v>
-      </c>
-      <c r="T10" t="n">
-        <v>35351</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.02526882</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.02766541</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.0583</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>235</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>393</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>422.8183</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1119.5017</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>5.2751</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="n">
-        <v>3421</v>
-      </c>
-      <c r="C11" t="n">
-        <v>128.431</v>
-      </c>
-      <c r="D11" t="n">
-        <v>34.9252</v>
-      </c>
-      <c r="E11" t="n">
-        <v>3.6773</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.9623</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.8774</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.2145</v>
-      </c>
-      <c r="I11" t="n">
-        <v>813.822</v>
-      </c>
-      <c r="J11" t="n">
-        <v>732.5244</v>
-      </c>
-      <c r="K11" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M11" t="n">
-        <v>405</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1142</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1149.7199</v>
-      </c>
-      <c r="P11" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>32.8491</v>
-      </c>
-      <c r="R11" t="n">
-        <v>326.8356</v>
-      </c>
-      <c r="S11" t="n">
-        <v>11837</v>
-      </c>
-      <c r="T11" t="n">
-        <v>29271</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.03421475</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.03901472</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.4477</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>300</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>682</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>453.6762</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1281.0874</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>5.6559</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="n">
-        <v>2890</v>
-      </c>
-      <c r="C12" t="n">
-        <v>110.8033</v>
-      </c>
-      <c r="D12" t="n">
-        <v>33.408</v>
-      </c>
-      <c r="E12" t="n">
-        <v>3.3167</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.9535</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.9298999999999999</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.0034</v>
-      </c>
-      <c r="I12" t="n">
-        <v>944.8156</v>
-      </c>
-      <c r="J12" t="n">
-        <v>407.9035</v>
-      </c>
-      <c r="K12" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>6</v>
-      </c>
-      <c r="M12" t="n">
-        <v>230</v>
-      </c>
-      <c r="N12" t="n">
-        <v>605</v>
-      </c>
-      <c r="O12" t="n">
-        <v>570.4874</v>
-      </c>
-      <c r="P12" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>35.6555</v>
-      </c>
-      <c r="R12" t="n">
-        <v>263.4802</v>
-      </c>
-      <c r="S12" t="n">
-        <v>9968</v>
-      </c>
-      <c r="T12" t="n">
-        <v>22850</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.9798</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.8783</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0.02307384</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.02647702</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.2772</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>138</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>209</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>254.865</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>671.2275</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>4.8394</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="n">
-        <v>508</v>
-      </c>
-      <c r="C13" t="n">
-        <v>44.3947</v>
-      </c>
-      <c r="D13" t="n">
-        <v>15.6697</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2.8331</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.9356</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.917</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-0.2083</v>
-      </c>
-      <c r="I13" t="n">
-        <v>990.1555</v>
-      </c>
-      <c r="J13" t="n">
-        <v>937.6988</v>
-      </c>
-      <c r="K13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>3</v>
-      </c>
-      <c r="M13" t="n">
-        <v>98</v>
-      </c>
-      <c r="N13" t="n">
-        <v>290</v>
-      </c>
-      <c r="O13" t="n">
-        <v>723.1981</v>
-      </c>
-      <c r="P13" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>28.9279</v>
-      </c>
-      <c r="R13" t="n">
-        <v>108.7696</v>
-      </c>
-      <c r="S13" t="n">
-        <v>5218</v>
-      </c>
-      <c r="T13" t="n">
-        <v>13093</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0.8837</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.01878114</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.02214924</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.7581</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>72</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>165</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>101.2843</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>311.7939</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>4.5752</v>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>why</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>it includes the optical blur, which widens a thread beyond its true size, and no point spread function is subtracted: the numerical aperture, the emission wavelength and the pinhole are unknown. It is an apparent width in the image, not a canalicular diameter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>median_um</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>p10_um</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>p90_um</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
@@ -3165,6 +2179,1399 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AG13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>lacuna_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>area_px2</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>major_axis_length_px</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>minor_axis_length_px</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>aspect_ratio</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eccentricity</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>solidity</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>orientation_rad</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>centroid_row_px</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>centroid_col_px</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>on_border</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>roots_count</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ring_length_r30_px</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ring_length_r60_px</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>owned_length_px</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>edge_count</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>mean_edge_length_px</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>perimeter_px</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ring_area_r30_px2</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ring_area_r60_px2</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r30</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r60</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>ring_density_r30</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>ring_density_r60</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>roots_per_100px_perimeter</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r30_px</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r60_px</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ring_length_w_r30_px</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ring_length_w_r60_px</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r10</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r20</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r30</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>ring_width_mean_r30_px</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>602</v>
+      </c>
+      <c r="C2" t="n">
+        <v>56.2113</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.2037</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.651</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9261</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6645</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.3574</v>
+      </c>
+      <c r="I2" t="n">
+        <v>16.2608</v>
+      </c>
+      <c r="J2" t="n">
+        <v>914.0415</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M2" t="n">
+        <v>194</v>
+      </c>
+      <c r="N2" t="n">
+        <v>525</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1057.7788</v>
+      </c>
+      <c r="P2" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>16.7901</v>
+      </c>
+      <c r="R2" t="n">
+        <v>142.8112</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4575</v>
+      </c>
+      <c r="T2" t="n">
+        <v>11641</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.6207</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.04240437</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.04509922</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.1007</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>187</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>370</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>222.1665</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>597.5584</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>6.0839</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5924</v>
+      </c>
+      <c r="C3" t="n">
+        <v>181.0427</v>
+      </c>
+      <c r="D3" t="n">
+        <v>48.2611</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.7513</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9638</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.0924</v>
+      </c>
+      <c r="I3" t="n">
+        <v>129.8709</v>
+      </c>
+      <c r="J3" t="n">
+        <v>638.6273</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>18</v>
+      </c>
+      <c r="M3" t="n">
+        <v>655</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1394</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2598.1871</v>
+      </c>
+      <c r="P3" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>20.2983</v>
+      </c>
+      <c r="R3" t="n">
+        <v>625.725</v>
+      </c>
+      <c r="S3" t="n">
+        <v>16860</v>
+      </c>
+      <c r="T3" t="n">
+        <v>35430</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.9542</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.8861</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.03884935</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.03934519</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.8767</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>621</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1151</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>741.1981</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1585.8641</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>7.0918</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4438</v>
+      </c>
+      <c r="C4" t="n">
+        <v>160.6807</v>
+      </c>
+      <c r="D4" t="n">
+        <v>35.4482</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.5328</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9754</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8989</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.2181</v>
+      </c>
+      <c r="I4" t="n">
+        <v>173.3515</v>
+      </c>
+      <c r="J4" t="n">
+        <v>382.514</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M4" t="n">
+        <v>309</v>
+      </c>
+      <c r="N4" t="n">
+        <v>852</v>
+      </c>
+      <c r="O4" t="n">
+        <v>884.8133</v>
+      </c>
+      <c r="P4" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>24.5781</v>
+      </c>
+      <c r="R4" t="n">
+        <v>377.0193</v>
+      </c>
+      <c r="S4" t="n">
+        <v>13152</v>
+      </c>
+      <c r="T4" t="n">
+        <v>31926</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.02349453</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.02668671</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.5914</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>202</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>490</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>336.6224</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>951.9382000000001</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>6.9032</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4342</v>
+      </c>
+      <c r="C5" t="n">
+        <v>127.7957</v>
+      </c>
+      <c r="D5" t="n">
+        <v>43.8553</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.914</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9393</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.1983</v>
+      </c>
+      <c r="I5" t="n">
+        <v>210.2996</v>
+      </c>
+      <c r="J5" t="n">
+        <v>874.1078</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>468</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1205</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3517.0126</v>
+      </c>
+      <c r="P5" t="n">
+        <v>152</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>23.1382</v>
+      </c>
+      <c r="R5" t="n">
+        <v>337.7056</v>
+      </c>
+      <c r="S5" t="n">
+        <v>12118</v>
+      </c>
+      <c r="T5" t="n">
+        <v>29514</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.03862023</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.04082808</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.3689</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>342</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>805</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>521.4041</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1386.0824</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>6.3053</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5254</v>
+      </c>
+      <c r="C6" t="n">
+        <v>148.6874</v>
+      </c>
+      <c r="D6" t="n">
+        <v>46.2758</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.2131</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9503</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9227</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.0688</v>
+      </c>
+      <c r="I6" t="n">
+        <v>369.2524</v>
+      </c>
+      <c r="J6" t="n">
+        <v>79.7008</v>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9</v>
+      </c>
+      <c r="M6" t="n">
+        <v>435</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1102</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3371.645</v>
+      </c>
+      <c r="P6" t="n">
+        <v>177</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>19.0488</v>
+      </c>
+      <c r="R6" t="n">
+        <v>371.8061</v>
+      </c>
+      <c r="S6" t="n">
+        <v>13199</v>
+      </c>
+      <c r="T6" t="n">
+        <v>31872</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.9956</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.03295704</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.0345758</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.4206</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>322</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>865</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>484.5046</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1246.389</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>7.4759</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3405</v>
+      </c>
+      <c r="C7" t="n">
+        <v>124.6016</v>
+      </c>
+      <c r="D7" t="n">
+        <v>35.4524</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.5146</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9587</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8958</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="I7" t="n">
+        <v>532.2396</v>
+      </c>
+      <c r="J7" t="n">
+        <v>401.3151</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>7</v>
+      </c>
+      <c r="M7" t="n">
+        <v>303</v>
+      </c>
+      <c r="N7" t="n">
+        <v>828</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1241.4722</v>
+      </c>
+      <c r="P7" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>24.8294</v>
+      </c>
+      <c r="R7" t="n">
+        <v>308.5929</v>
+      </c>
+      <c r="S7" t="n">
+        <v>11379</v>
+      </c>
+      <c r="T7" t="n">
+        <v>28385</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.026628</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.02917034</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.2684</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>219</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>557</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>337.0071</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>944.5361</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>6.5001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4133</v>
+      </c>
+      <c r="C8" t="n">
+        <v>149.9613</v>
+      </c>
+      <c r="D8" t="n">
+        <v>37.557</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.9929</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9681</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.1428</v>
+      </c>
+      <c r="I8" t="n">
+        <v>589.0707</v>
+      </c>
+      <c r="J8" t="n">
+        <v>924.0489</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>513</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1421</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2815.8439</v>
+      </c>
+      <c r="P8" t="n">
+        <v>141</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>19.9705</v>
+      </c>
+      <c r="R8" t="n">
+        <v>382.8772</v>
+      </c>
+      <c r="S8" t="n">
+        <v>12760</v>
+      </c>
+      <c r="T8" t="n">
+        <v>30245</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.04020376</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.04698297</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.0894</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>423</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1257</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>583.9016</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1597.6976</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>6.9486</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2572</v>
+      </c>
+      <c r="C9" t="n">
+        <v>119.2938</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30.2433</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.9445</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9673</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8307</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="I9" t="n">
+        <v>570.0315000000001</v>
+      </c>
+      <c r="J9" t="n">
+        <v>785.133</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>311</v>
+      </c>
+      <c r="N9" t="n">
+        <v>929</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1062.2224</v>
+      </c>
+      <c r="P9" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>32.1886</v>
+      </c>
+      <c r="R9" t="n">
+        <v>306.4924</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10697</v>
+      </c>
+      <c r="T9" t="n">
+        <v>26160</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.02907357</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.03551223</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.6102</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>164</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>312</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>333.6518</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1032.2813</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>6.6332</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3684</v>
+      </c>
+      <c r="C10" t="n">
+        <v>159.3366</v>
+      </c>
+      <c r="D10" t="n">
+        <v>32.9692</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4.8329</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9784</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8054</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.098</v>
+      </c>
+      <c r="I10" t="n">
+        <v>739.4517</v>
+      </c>
+      <c r="J10" t="n">
+        <v>247.5361</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M10" t="n">
+        <v>348</v>
+      </c>
+      <c r="N10" t="n">
+        <v>851</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1584.5088</v>
+      </c>
+      <c r="P10" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>23.3016</v>
+      </c>
+      <c r="R10" t="n">
+        <v>437.262</v>
+      </c>
+      <c r="S10" t="n">
+        <v>14880</v>
+      </c>
+      <c r="T10" t="n">
+        <v>35351</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.0233871</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.02407287</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.6009</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>312</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>550</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>398.7767</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>971.0509</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>5.5018</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3421</v>
+      </c>
+      <c r="C11" t="n">
+        <v>128.431</v>
+      </c>
+      <c r="D11" t="n">
+        <v>34.9252</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.6773</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9623</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8774</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.2145</v>
+      </c>
+      <c r="I11" t="n">
+        <v>813.822</v>
+      </c>
+      <c r="J11" t="n">
+        <v>732.5244</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>11</v>
+      </c>
+      <c r="M11" t="n">
+        <v>420</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1250</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3061.8978</v>
+      </c>
+      <c r="P11" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>22.6807</v>
+      </c>
+      <c r="R11" t="n">
+        <v>326.8356</v>
+      </c>
+      <c r="S11" t="n">
+        <v>11837</v>
+      </c>
+      <c r="T11" t="n">
+        <v>29271</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.03548196</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.04270438</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.3656</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>348</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>917</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>464.8478</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1402.7443</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>6.5998</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2890</v>
+      </c>
+      <c r="C12" t="n">
+        <v>110.8033</v>
+      </c>
+      <c r="D12" t="n">
+        <v>33.408</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.3167</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9535</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9298999999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="I12" t="n">
+        <v>944.8156</v>
+      </c>
+      <c r="J12" t="n">
+        <v>407.9035</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>223</v>
+      </c>
+      <c r="N12" t="n">
+        <v>635</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1131.0631</v>
+      </c>
+      <c r="P12" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>26.9301</v>
+      </c>
+      <c r="R12" t="n">
+        <v>263.4802</v>
+      </c>
+      <c r="S12" t="n">
+        <v>9968</v>
+      </c>
+      <c r="T12" t="n">
+        <v>22850</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.9798</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.8783</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.02237159</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.02778993</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.8977</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>124</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>237</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>248.5513</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>713.127</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>6.5688</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>508</v>
+      </c>
+      <c r="C13" t="n">
+        <v>44.3947</v>
+      </c>
+      <c r="D13" t="n">
+        <v>15.6697</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.8331</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9356</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.2083</v>
+      </c>
+      <c r="I13" t="n">
+        <v>990.1555</v>
+      </c>
+      <c r="J13" t="n">
+        <v>937.6988</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" t="n">
+        <v>103</v>
+      </c>
+      <c r="N13" t="n">
+        <v>301</v>
+      </c>
+      <c r="O13" t="n">
+        <v>840.4651</v>
+      </c>
+      <c r="P13" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>30.0166</v>
+      </c>
+      <c r="R13" t="n">
+        <v>108.7696</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5218</v>
+      </c>
+      <c r="T13" t="n">
+        <v>13093</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.8837</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.01973936</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.02298938</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>3.6775</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>77</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>167</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>107.1127</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>328.4508</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>5.2586</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -3185,7 +3592,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Measured only on skeleton pixels with real signal under them: bridged pixels, the lacuna buffer and the</t>
+          <t>Measured only on skeleton pixels on the canalicular mask: the lacuna buffer and the</t>
         </is>
       </c>
     </row>

--- a/results/542_z18/5_quantification/542_z18_quantification.xlsx
+++ b/results/542_z18/5_quantification/542_z18_quantification.xlsx
@@ -460,10 +460,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>11</v>
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8.2727</v>
+        <v>6.1818</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>3.7441</v>
+        <v>5.1927</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>371.6364</v>
+        <v>399.2727</v>
       </c>
       <c r="D13" t="n">
-        <v>348</v>
+        <v>403</v>
       </c>
       <c r="E13" t="n">
-        <v>149.3474</v>
+        <v>153.861</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>978.9091</v>
+        <v>1055.1818</v>
       </c>
       <c r="D14" t="n">
-        <v>929</v>
+        <v>1100</v>
       </c>
       <c r="E14" t="n">
-        <v>338.093</v>
+        <v>357.6204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2009.921</v>
+        <v>2242.8543</v>
       </c>
       <c r="D15" t="n">
-        <v>1584.5088</v>
+        <v>2419.6114</v>
       </c>
       <c r="E15" t="n">
-        <v>1063.1721</v>
+        <v>1365.9988</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>90</v>
+        <v>101.3636</v>
       </c>
       <c r="D16" t="n">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="E16" t="n">
-        <v>56.4624</v>
+        <v>63.0782</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.271</v>
+        <v>22.5943</v>
       </c>
       <c r="D17" t="n">
-        <v>23.3016</v>
+        <v>21.6037</v>
       </c>
       <c r="E17" t="n">
-        <v>4.1168</v>
+        <v>4.124</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>12006.1818</v>
+        <v>11901.1818</v>
       </c>
       <c r="D19" t="n">
         <v>12118</v>
       </c>
       <c r="E19" t="n">
-        <v>2958.1139</v>
+        <v>3231.0652</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28554.2727</v>
+        <v>28359.3636</v>
       </c>
       <c r="D20" t="n">
         <v>29514</v>
       </c>
       <c r="E20" t="n">
-        <v>6304.6903</v>
+        <v>6840.8186</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.03007332</v>
+        <v>0.03273455</v>
       </c>
       <c r="D23" t="n">
-        <v>0.02907357</v>
+        <v>0.03212365</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00746476</v>
+        <v>0.00693422</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.03369617</v>
+        <v>0.03657206</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0345758</v>
+        <v>0.03715596</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00810109</v>
+        <v>0.00790943</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.4334</v>
+        <v>1.6497</v>
       </c>
       <c r="D25" t="n">
-        <v>2.3689</v>
+        <v>1.6009</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6696</v>
+        <v>0.8214</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>286.7273</v>
+        <v>314.9091</v>
       </c>
       <c r="D26" t="n">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="E26" t="n">
-        <v>153.7186</v>
+        <v>163.2038</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>664.3636</v>
+        <v>786</v>
       </c>
       <c r="D27" t="n">
-        <v>557</v>
+        <v>794</v>
       </c>
       <c r="E27" t="n">
-        <v>363.4653</v>
+        <v>380.7936</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>414.3253</v>
+        <v>444.7003</v>
       </c>
       <c r="D28" t="n">
-        <v>398.7767</v>
+        <v>443.9777</v>
       </c>
       <c r="E28" t="n">
-        <v>171.8057</v>
+        <v>175.736</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1105.4692</v>
+        <v>1189.7529</v>
       </c>
       <c r="D29" t="n">
-        <v>1032.2813</v>
+        <v>1240.1758</v>
       </c>
       <c r="E29" t="n">
-        <v>386.0866</v>
+        <v>409.8646</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9.0909</v>
+        <v>9.545500000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>5.0091</v>
+        <v>5.2605</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13</v>
+        <v>14.1818</v>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E31" t="n">
-        <v>5.0794</v>
+        <v>6.29</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>15</v>
+        <v>15.8182</v>
       </c>
       <c r="D32" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E32" t="n">
-        <v>5.2536</v>
+        <v>5.3818</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6.5261</v>
+        <v>7.355</v>
       </c>
       <c r="D33" t="n">
-        <v>6.5998</v>
+        <v>7.398</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6532</v>
+        <v>0.5346</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1007403</v>
+        <v>1007168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>34260</v>
+        <v>36672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03400824</v>
+        <v>0.03641101</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>701</v>
+        <v>777</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00069585</v>
+        <v>0.00077147</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.191e-05</v>
+        <v>1.291e-05</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>123.6823</v>
+        <v>148.4696</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03846082</v>
+        <v>0.04114015</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0338477</v>
+        <v>0.03634245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1613,6 +1613,86 @@
         </is>
       </c>
       <c r="D14" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>unattached_length_px</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>372</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>unattached_component_count</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>22</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>canalicular_length_density_attached_per_px</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.03641101</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>field_length_density_with_unattached_per_px</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.03678036</v>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>px^-1</t>
         </is>
@@ -1666,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.3706</v>
+        <v>8.0998</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1686,7 +1766,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>8.2462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1706,7 +1786,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>4.4721</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1726,7 +1806,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>10.7703</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1746,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32773</v>
+        <v>35180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1889,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>516</v>
+        <v>586</v>
       </c>
     </row>
     <row r="9">
@@ -1904,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.6909</v>
+        <v>20.9928</v>
       </c>
     </row>
     <row r="10">
@@ -1919,7 +1999,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.39</v>
+        <v>0.4438</v>
       </c>
     </row>
     <row r="11">
@@ -1934,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>40.0725</v>
+        <v>44.189</v>
       </c>
     </row>
     <row r="12">
@@ -1949,7 +2029,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>50.0433</v>
+        <v>50.0379</v>
       </c>
     </row>
     <row r="13">
@@ -1964,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.3547</v>
+        <v>0.3908</v>
       </c>
     </row>
     <row r="14">
@@ -1979,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6453</v>
+        <v>0.6092</v>
       </c>
     </row>
     <row r="15">
@@ -2041,7 +2121,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2056,7 +2136,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2071,7 +2151,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -2135,7 +2215,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.04</v>
+        <v>1.072</v>
       </c>
     </row>
     <row r="25">
@@ -2150,7 +2230,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.52</v>
+        <v>0.5814</v>
       </c>
     </row>
     <row r="26">
@@ -2165,7 +2245,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.3</v>
+        <v>1.4001</v>
       </c>
     </row>
   </sheetData>
@@ -2179,7 +2259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG13"/>
+  <dimension ref="A1:AG14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2384,22 +2464,22 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="N2" t="n">
-        <v>525</v>
+        <v>584</v>
       </c>
       <c r="O2" t="n">
-        <v>1057.7788</v>
+        <v>872.4823</v>
       </c>
       <c r="P2" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="Q2" t="n">
-        <v>16.7901</v>
+        <v>18.1767</v>
       </c>
       <c r="R2" t="n">
         <v>142.8112</v>
@@ -2417,25 +2497,25 @@
         <v>0.6207</v>
       </c>
       <c r="W2" t="n">
-        <v>0.04240437</v>
+        <v>0.04786885</v>
       </c>
       <c r="X2" t="n">
-        <v>0.04509922</v>
+        <v>0.05016751</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.1007</v>
+        <v>1.4005</v>
       </c>
       <c r="Z2" t="n">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="AA2" t="n">
-        <v>370</v>
+        <v>456</v>
       </c>
       <c r="AB2" t="n">
-        <v>222.1665</v>
+        <v>249.8234</v>
       </c>
       <c r="AC2" t="n">
-        <v>597.5584</v>
+        <v>658.1442</v>
       </c>
       <c r="AD2" t="n">
         <v>4</v>
@@ -2444,10 +2524,10 @@
         <v>7</v>
       </c>
       <c r="AF2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG2" t="n">
-        <v>6.0839</v>
+        <v>7.3357</v>
       </c>
     </row>
     <row r="3">
@@ -2485,22 +2565,22 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M3" t="n">
-        <v>655</v>
+        <v>684</v>
       </c>
       <c r="N3" t="n">
-        <v>1394</v>
+        <v>1477</v>
       </c>
       <c r="O3" t="n">
-        <v>2598.1871</v>
+        <v>3155.2064</v>
       </c>
       <c r="P3" t="n">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.2983</v>
+        <v>19.72</v>
       </c>
       <c r="R3" t="n">
         <v>625.725</v>
@@ -2518,37 +2598,37 @@
         <v>0.8861</v>
       </c>
       <c r="W3" t="n">
-        <v>0.03884935</v>
+        <v>0.0405694</v>
       </c>
       <c r="X3" t="n">
-        <v>0.03934519</v>
+        <v>0.04168784</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.8767</v>
+        <v>3.1963</v>
       </c>
       <c r="Z3" t="n">
-        <v>621</v>
+        <v>664</v>
       </c>
       <c r="AA3" t="n">
-        <v>1151</v>
+        <v>1234</v>
       </c>
       <c r="AB3" t="n">
-        <v>741.1981</v>
+        <v>774.0975</v>
       </c>
       <c r="AC3" t="n">
-        <v>1585.8641</v>
+        <v>1686.3911</v>
       </c>
       <c r="AD3" t="n">
         <v>22</v>
       </c>
       <c r="AE3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AF3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG3" t="n">
-        <v>7.0918</v>
+        <v>7.4739</v>
       </c>
     </row>
     <row r="4">
@@ -2586,22 +2666,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>309</v>
+        <v>403</v>
       </c>
       <c r="N4" t="n">
-        <v>852</v>
+        <v>1085</v>
       </c>
       <c r="O4" t="n">
-        <v>884.8133</v>
+        <v>739.6589</v>
       </c>
       <c r="P4" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="Q4" t="n">
-        <v>24.5781</v>
+        <v>32.1591</v>
       </c>
       <c r="R4" t="n">
         <v>377.0193</v>
@@ -2619,37 +2699,37 @@
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02349453</v>
+        <v>0.03064173</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02668671</v>
+        <v>0.03398484</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.5914</v>
+        <v>0.7957</v>
       </c>
       <c r="Z4" t="n">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="AA4" t="n">
-        <v>490</v>
+        <v>756</v>
       </c>
       <c r="AB4" t="n">
-        <v>336.6224</v>
+        <v>443.9777</v>
       </c>
       <c r="AC4" t="n">
-        <v>951.9382000000001</v>
+        <v>1207.6488</v>
       </c>
       <c r="AD4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AF4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AG4" t="n">
-        <v>6.9032</v>
+        <v>7.5955</v>
       </c>
     </row>
     <row r="5">
@@ -2687,22 +2767,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M5" t="n">
-        <v>468</v>
+        <v>488</v>
       </c>
       <c r="N5" t="n">
-        <v>1205</v>
+        <v>1259</v>
       </c>
       <c r="O5" t="n">
-        <v>3517.0126</v>
+        <v>3854.1669</v>
       </c>
       <c r="P5" t="n">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="Q5" t="n">
-        <v>23.1382</v>
+        <v>22.2784</v>
       </c>
       <c r="R5" t="n">
         <v>337.7056</v>
@@ -2720,37 +2800,37 @@
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03862023</v>
+        <v>0.04027067</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04082808</v>
+        <v>0.04265772</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.3689</v>
+        <v>2.9612</v>
       </c>
       <c r="Z5" t="n">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="AA5" t="n">
-        <v>805</v>
+        <v>853</v>
       </c>
       <c r="AB5" t="n">
-        <v>521.4041</v>
+        <v>541.4041</v>
       </c>
       <c r="AC5" t="n">
-        <v>1386.0824</v>
+        <v>1440.3545</v>
       </c>
       <c r="AD5" t="n">
         <v>10</v>
       </c>
       <c r="AE5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF5" t="n">
         <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>6.3053</v>
+        <v>7.3773</v>
       </c>
     </row>
     <row r="6">
@@ -2788,22 +2868,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="N6" t="n">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="O6" t="n">
-        <v>3371.645</v>
+        <v>2973.7434</v>
       </c>
       <c r="P6" t="n">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="Q6" t="n">
-        <v>19.0488</v>
+        <v>19.5641</v>
       </c>
       <c r="R6" t="n">
         <v>371.8061</v>
@@ -2821,37 +2901,37 @@
         <v>0.9956</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03295704</v>
+        <v>0.03212365</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0345758</v>
+        <v>0.03451305</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.4206</v>
+        <v>1.6137</v>
       </c>
       <c r="Z6" t="n">
-        <v>322</v>
+        <v>301</v>
       </c>
       <c r="AA6" t="n">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="AB6" t="n">
-        <v>484.5046</v>
+        <v>470.1198</v>
       </c>
       <c r="AC6" t="n">
-        <v>1246.389</v>
+        <v>1240.1758</v>
       </c>
       <c r="AD6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG6" t="n">
-        <v>7.4759</v>
+        <v>8.1648</v>
       </c>
     </row>
     <row r="7">
@@ -2889,22 +2969,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>303</v>
+        <v>385</v>
       </c>
       <c r="N7" t="n">
-        <v>828</v>
+        <v>1117</v>
       </c>
       <c r="O7" t="n">
-        <v>1241.4722</v>
+        <v>3650.711</v>
       </c>
       <c r="P7" t="n">
-        <v>50</v>
+        <v>159</v>
       </c>
       <c r="Q7" t="n">
-        <v>24.8294</v>
+        <v>22.9604</v>
       </c>
       <c r="R7" t="n">
         <v>308.5929</v>
@@ -2922,37 +3002,37 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.026628</v>
+        <v>0.03383426</v>
       </c>
       <c r="X7" t="n">
-        <v>0.02917034</v>
+        <v>0.03935177</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.2684</v>
+        <v>1.6203</v>
       </c>
       <c r="Z7" t="n">
-        <v>219</v>
+        <v>294</v>
       </c>
       <c r="AA7" t="n">
-        <v>557</v>
+        <v>794</v>
       </c>
       <c r="AB7" t="n">
-        <v>337.0071</v>
+        <v>429.3625</v>
       </c>
       <c r="AC7" t="n">
-        <v>944.5361</v>
+        <v>1277.9575</v>
       </c>
       <c r="AD7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AG7" t="n">
-        <v>6.5001</v>
+        <v>7.1407</v>
       </c>
     </row>
     <row r="8">
@@ -2990,22 +3070,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M8" t="n">
-        <v>513</v>
+        <v>535</v>
       </c>
       <c r="N8" t="n">
-        <v>1421</v>
+        <v>1476</v>
       </c>
       <c r="O8" t="n">
-        <v>2815.8439</v>
+        <v>1773.7931</v>
       </c>
       <c r="P8" t="n">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="Q8" t="n">
-        <v>19.9705</v>
+        <v>21.1166</v>
       </c>
       <c r="R8" t="n">
         <v>382.8772</v>
@@ -3023,37 +3103,37 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.04020376</v>
+        <v>0.0419279</v>
       </c>
       <c r="X8" t="n">
-        <v>0.04698297</v>
+        <v>0.04880145</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.0894</v>
+        <v>1.3059</v>
       </c>
       <c r="Z8" t="n">
-        <v>423</v>
+        <v>471</v>
       </c>
       <c r="AA8" t="n">
-        <v>1257</v>
+        <v>1307</v>
       </c>
       <c r="AB8" t="n">
-        <v>583.9016</v>
+        <v>601.4163</v>
       </c>
       <c r="AC8" t="n">
-        <v>1597.6976</v>
+        <v>1660.8692</v>
       </c>
       <c r="AD8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF8" t="n">
         <v>20</v>
       </c>
-      <c r="AF8" t="n">
-        <v>22</v>
-      </c>
       <c r="AG8" t="n">
-        <v>6.9486</v>
+        <v>7.9782</v>
       </c>
     </row>
     <row r="9">
@@ -3091,22 +3171,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>311</v>
+        <v>338</v>
       </c>
       <c r="N9" t="n">
-        <v>929</v>
+        <v>972</v>
       </c>
       <c r="O9" t="n">
-        <v>1062.2224</v>
+        <v>2419.6114</v>
       </c>
       <c r="P9" t="n">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="Q9" t="n">
-        <v>32.1886</v>
+        <v>21.6037</v>
       </c>
       <c r="R9" t="n">
         <v>306.4924</v>
@@ -3124,37 +3204,37 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02907357</v>
+        <v>0.03159764</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03551223</v>
+        <v>0.03715596</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.6102</v>
+        <v>1.3051</v>
       </c>
       <c r="Z9" t="n">
-        <v>164</v>
+        <v>216</v>
       </c>
       <c r="AA9" t="n">
-        <v>312</v>
+        <v>555</v>
       </c>
       <c r="AB9" t="n">
-        <v>333.6518</v>
+        <v>367.865</v>
       </c>
       <c r="AC9" t="n">
-        <v>1032.2813</v>
+        <v>1080.2519</v>
       </c>
       <c r="AD9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF9" t="n">
         <v>15</v>
       </c>
       <c r="AG9" t="n">
-        <v>6.6332</v>
+        <v>7.3532</v>
       </c>
     </row>
     <row r="10">
@@ -3195,19 +3275,19 @@
         <v>7</v>
       </c>
       <c r="M10" t="n">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="N10" t="n">
-        <v>851</v>
+        <v>878</v>
       </c>
       <c r="O10" t="n">
-        <v>1584.5088</v>
+        <v>1474.5139</v>
       </c>
       <c r="P10" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Q10" t="n">
-        <v>23.3016</v>
+        <v>21.3698</v>
       </c>
       <c r="R10" t="n">
         <v>437.262</v>
@@ -3225,25 +3305,25 @@
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0233871</v>
+        <v>0.02452957</v>
       </c>
       <c r="X10" t="n">
-        <v>0.02407287</v>
+        <v>0.02483664</v>
       </c>
       <c r="Y10" t="n">
         <v>1.6009</v>
       </c>
       <c r="Z10" t="n">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="AA10" t="n">
-        <v>550</v>
+        <v>651</v>
       </c>
       <c r="AB10" t="n">
-        <v>398.7767</v>
+        <v>415.463</v>
       </c>
       <c r="AC10" t="n">
-        <v>971.0509</v>
+        <v>998.9087</v>
       </c>
       <c r="AD10" t="n">
         <v>12</v>
@@ -3255,7 +3335,7 @@
         <v>13</v>
       </c>
       <c r="AG10" t="n">
-        <v>5.5018</v>
+        <v>6.5411</v>
       </c>
     </row>
     <row r="11">
@@ -3293,22 +3373,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="M11" t="n">
-        <v>420</v>
+        <v>448</v>
       </c>
       <c r="N11" t="n">
-        <v>1250</v>
+        <v>1323</v>
       </c>
       <c r="O11" t="n">
-        <v>3061.8978</v>
+        <v>3831.2968</v>
       </c>
       <c r="P11" t="n">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="Q11" t="n">
-        <v>22.6807</v>
+        <v>25.2059</v>
       </c>
       <c r="R11" t="n">
         <v>326.8356</v>
@@ -3326,37 +3406,37 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.03548196</v>
+        <v>0.03784743</v>
       </c>
       <c r="X11" t="n">
-        <v>0.04270438</v>
+        <v>0.04519832</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.3656</v>
+        <v>1.5298</v>
       </c>
       <c r="Z11" t="n">
-        <v>348</v>
+        <v>390</v>
       </c>
       <c r="AA11" t="n">
-        <v>917</v>
+        <v>1236</v>
       </c>
       <c r="AB11" t="n">
-        <v>464.8478</v>
+        <v>498.5757</v>
       </c>
       <c r="AC11" t="n">
-        <v>1402.7443</v>
+        <v>1479.7443</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
         <v>16</v>
       </c>
       <c r="AF11" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AG11" t="n">
-        <v>6.5998</v>
+        <v>7.5279</v>
       </c>
     </row>
     <row r="12">
@@ -3394,22 +3474,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>223</v>
       </c>
       <c r="N12" t="n">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="O12" t="n">
-        <v>1131.0631</v>
+        <v>16.4853</v>
       </c>
       <c r="P12" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>26.9301</v>
+        <v>16.4853</v>
       </c>
       <c r="R12" t="n">
         <v>263.4802</v>
@@ -3430,34 +3510,34 @@
         <v>0.02237159</v>
       </c>
       <c r="X12" t="n">
-        <v>0.02778993</v>
+        <v>0.02752735</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.8977</v>
+        <v>0.3795</v>
       </c>
       <c r="Z12" t="n">
         <v>124</v>
       </c>
       <c r="AA12" t="n">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="AB12" t="n">
-        <v>248.5513</v>
+        <v>245.7229</v>
       </c>
       <c r="AC12" t="n">
-        <v>713.127</v>
+        <v>700.328</v>
       </c>
       <c r="AD12" t="n">
         <v>5</v>
       </c>
       <c r="AE12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF12" t="n">
         <v>8</v>
       </c>
       <c r="AG12" t="n">
-        <v>6.5688</v>
+        <v>7.398</v>
       </c>
     </row>
     <row r="13">
@@ -3495,31 +3575,31 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="N13" t="n">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="O13" t="n">
-        <v>840.4651</v>
+        <v>782.2102</v>
       </c>
       <c r="P13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q13" t="n">
-        <v>30.0166</v>
+        <v>26.0737</v>
       </c>
       <c r="R13" t="n">
         <v>108.7696</v>
       </c>
       <c r="S13" t="n">
-        <v>5218</v>
+        <v>4063</v>
       </c>
       <c r="T13" t="n">
-        <v>13093</v>
+        <v>10949</v>
       </c>
       <c r="U13" t="n">
         <v>0.8837</v>
@@ -3528,28 +3608,28 @@
         <v>0.75</v>
       </c>
       <c r="W13" t="n">
-        <v>0.01973936</v>
+        <v>0.02436623</v>
       </c>
       <c r="X13" t="n">
-        <v>0.02298938</v>
+        <v>0.02657777</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.6775</v>
+        <v>1.8387</v>
       </c>
       <c r="Z13" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="AA13" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AB13" t="n">
-        <v>107.1127</v>
+        <v>103.6985</v>
       </c>
       <c r="AC13" t="n">
-        <v>328.4508</v>
+        <v>314.6518</v>
       </c>
       <c r="AD13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
@@ -3558,7 +3638,84 @@
         <v>5</v>
       </c>
       <c r="AG13" t="n">
-        <v>5.2586</v>
+        <v>6.3545</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1015.1447</v>
+      </c>
+      <c r="J14" t="n">
+        <v>933.9021</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>9</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>59.8995</v>
+      </c>
+      <c r="S14" t="n">
+        <v>971</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1939</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.6158</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.5712</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.00464157</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>10.0711</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/results/542_z18/5_quantification/542_z18_quantification.xlsx
+++ b/results/542_z18/5_quantification/542_z18_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.1818</v>
+        <v>8.3636</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>5.1927</v>
+        <v>5.0452</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>399.2727</v>
+        <v>400.5455</v>
       </c>
       <c r="D13" t="n">
         <v>403</v>
       </c>
       <c r="E13" t="n">
-        <v>153.861</v>
+        <v>155.5618</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1055.1818</v>
+        <v>1056.4545</v>
       </c>
       <c r="D14" t="n">
         <v>1100</v>
       </c>
       <c r="E14" t="n">
-        <v>357.6204</v>
+        <v>360.6065</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2242.8543</v>
+        <v>2428.7597</v>
       </c>
       <c r="D15" t="n">
-        <v>2419.6114</v>
+        <v>2591.8368</v>
       </c>
       <c r="E15" t="n">
-        <v>1365.9988</v>
+        <v>1179.0644</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>101.3636</v>
+        <v>106.3636</v>
       </c>
       <c r="D16" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E16" t="n">
-        <v>63.0782</v>
+        <v>56.5337</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.5943</v>
+        <v>24.5953</v>
       </c>
       <c r="D17" t="n">
-        <v>21.6037</v>
+        <v>22.9604</v>
       </c>
       <c r="E17" t="n">
-        <v>4.124</v>
+        <v>4.7993</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.03273455</v>
+        <v>0.03283017</v>
       </c>
       <c r="D23" t="n">
         <v>0.03212365</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00693422</v>
+        <v>0.00712545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.03657206</v>
+        <v>0.03660992</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03715596</v>
+        <v>0.03681193</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00790943</v>
+        <v>0.008027889999999999</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.6497</v>
+        <v>2.3523</v>
       </c>
       <c r="D25" t="n">
-        <v>1.6009</v>
+        <v>2.1517</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8214</v>
+        <v>0.8814</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>314.9091</v>
+        <v>319.5455</v>
       </c>
       <c r="D26" t="n">
         <v>301</v>
       </c>
       <c r="E26" t="n">
-        <v>163.2038</v>
+        <v>163.1394</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>786</v>
+        <v>799.1818</v>
       </c>
       <c r="D27" t="n">
         <v>794</v>
       </c>
       <c r="E27" t="n">
-        <v>380.7936</v>
+        <v>378.3043</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>444.7003</v>
+        <v>446.3275</v>
       </c>
       <c r="D28" t="n">
         <v>443.9777</v>
       </c>
       <c r="E28" t="n">
-        <v>175.736</v>
+        <v>177.6887</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1189.7529</v>
+        <v>1190.8061</v>
       </c>
       <c r="D29" t="n">
         <v>1240.1758</v>
       </c>
       <c r="E29" t="n">
-        <v>409.8646</v>
+        <v>412.4413</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.355</v>
+        <v>7.4383</v>
       </c>
       <c r="D33" t="n">
-        <v>7.398</v>
+        <v>7.4739</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5346</v>
+        <v>0.6045</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36672</v>
+        <v>36688</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03641101</v>
+        <v>0.03642689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00077147</v>
+        <v>0.00077048</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>148.4696</v>
+        <v>149.1382</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.04114015</v>
+        <v>0.04115446</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03634245</v>
+        <v>0.03635898</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03641101</v>
+        <v>0.03642689</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03678036</v>
+        <v>0.03679624</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.0998</v>
+        <v>8.1313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35180</v>
+        <v>35196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>586</v>
+        <v>596</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.9928</v>
+        <v>20.9797</v>
       </c>
     </row>
     <row r="10">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>44.189</v>
+        <v>43.9513</v>
       </c>
     </row>
     <row r="12">
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.3908</v>
+        <v>0.3876</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6092</v>
+        <v>0.6124000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -2464,7 +2464,7 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
         <v>219</v>
@@ -2473,13 +2473,13 @@
         <v>584</v>
       </c>
       <c r="O2" t="n">
-        <v>872.4823</v>
+        <v>1129.2641</v>
       </c>
       <c r="P2" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="Q2" t="n">
-        <v>18.1767</v>
+        <v>17.3733</v>
       </c>
       <c r="R2" t="n">
         <v>142.8112</v>
@@ -2503,7 +2503,7 @@
         <v>0.05016751</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.4005</v>
+        <v>2.1007</v>
       </c>
       <c r="Z2" t="n">
         <v>212</v>
@@ -2666,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
         <v>403</v>
@@ -2675,13 +2675,13 @@
         <v>1085</v>
       </c>
       <c r="O4" t="n">
-        <v>739.6589</v>
+        <v>778.2864</v>
       </c>
       <c r="P4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q4" t="n">
-        <v>32.1591</v>
+        <v>32.4286</v>
       </c>
       <c r="R4" t="n">
         <v>377.0193</v>
@@ -2705,7 +2705,7 @@
         <v>0.03398484</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.7957</v>
+        <v>1.061</v>
       </c>
       <c r="Z4" t="n">
         <v>238</v>
@@ -2767,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M5" t="n">
         <v>488</v>
@@ -2776,13 +2776,13 @@
         <v>1259</v>
       </c>
       <c r="O5" t="n">
-        <v>3854.1669</v>
+        <v>3608.8704</v>
       </c>
       <c r="P5" t="n">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.2784</v>
+        <v>22.9864</v>
       </c>
       <c r="R5" t="n">
         <v>337.7056</v>
@@ -2806,7 +2806,7 @@
         <v>0.04265772</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.9612</v>
+        <v>4.1456</v>
       </c>
       <c r="Z5" t="n">
         <v>365</v>
@@ -2830,7 +2830,7 @@
         <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>7.3773</v>
+        <v>7.4471</v>
       </c>
     </row>
     <row r="6">
@@ -2868,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
         <v>424</v>
@@ -2907,7 +2907,7 @@
         <v>0.03451305</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.6137</v>
+        <v>2.1517</v>
       </c>
       <c r="Z6" t="n">
         <v>301</v>
@@ -2969,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
         <v>385</v>
@@ -3008,7 +3008,7 @@
         <v>0.03935177</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.6203</v>
+        <v>1.9443</v>
       </c>
       <c r="Z7" t="n">
         <v>294</v>
@@ -3070,22 +3070,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>535</v>
+        <v>552</v>
       </c>
       <c r="N8" t="n">
-        <v>1476</v>
+        <v>1499</v>
       </c>
       <c r="O8" t="n">
-        <v>1773.7931</v>
+        <v>2365.9962</v>
       </c>
       <c r="P8" t="n">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="Q8" t="n">
-        <v>21.1166</v>
+        <v>22.1121</v>
       </c>
       <c r="R8" t="n">
         <v>382.8772</v>
@@ -3103,25 +3103,25 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0419279</v>
+        <v>0.04326019</v>
       </c>
       <c r="X8" t="n">
-        <v>0.04880145</v>
+        <v>0.04956191</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3059</v>
+        <v>2.3506</v>
       </c>
       <c r="Z8" t="n">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="AA8" t="n">
-        <v>1307</v>
+        <v>1330</v>
       </c>
       <c r="AB8" t="n">
-        <v>601.4163</v>
+        <v>621.0732</v>
       </c>
       <c r="AC8" t="n">
-        <v>1660.8692</v>
+        <v>1680.6266</v>
       </c>
       <c r="AD8" t="n">
         <v>12</v>
@@ -3133,7 +3133,7 @@
         <v>20</v>
       </c>
       <c r="AG8" t="n">
-        <v>7.9782</v>
+        <v>8.4041</v>
       </c>
     </row>
     <row r="9">
@@ -3171,22 +3171,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M9" t="n">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="N9" t="n">
-        <v>972</v>
+        <v>963</v>
       </c>
       <c r="O9" t="n">
-        <v>2419.6114</v>
+        <v>2591.8368</v>
       </c>
       <c r="P9" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="Q9" t="n">
-        <v>21.6037</v>
+        <v>22.3434</v>
       </c>
       <c r="R9" t="n">
         <v>306.4924</v>
@@ -3204,25 +3204,25 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03159764</v>
+        <v>0.03131719</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03715596</v>
+        <v>0.03681193</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3051</v>
+        <v>1.6314</v>
       </c>
       <c r="Z9" t="n">
-        <v>216</v>
+        <v>250</v>
       </c>
       <c r="AA9" t="n">
-        <v>555</v>
+        <v>677</v>
       </c>
       <c r="AB9" t="n">
-        <v>367.865</v>
+        <v>365.6934</v>
       </c>
       <c r="AC9" t="n">
-        <v>1080.2519</v>
+        <v>1071.6661</v>
       </c>
       <c r="AD9" t="n">
         <v>9</v>
@@ -3234,7 +3234,7 @@
         <v>15</v>
       </c>
       <c r="AG9" t="n">
-        <v>7.3532</v>
+        <v>7.7095</v>
       </c>
     </row>
     <row r="10">
@@ -3272,7 +3272,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M10" t="n">
         <v>365</v>
@@ -3311,7 +3311,7 @@
         <v>0.02483664</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.6009</v>
+        <v>2.0583</v>
       </c>
       <c r="Z10" t="n">
         <v>329</v>
@@ -3373,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M11" t="n">
         <v>448</v>
@@ -3382,13 +3382,13 @@
         <v>1323</v>
       </c>
       <c r="O11" t="n">
-        <v>3831.2968</v>
+        <v>4044.4928</v>
       </c>
       <c r="P11" t="n">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="Q11" t="n">
-        <v>25.2059</v>
+        <v>25.4371</v>
       </c>
       <c r="R11" t="n">
         <v>326.8356</v>
@@ -3412,7 +3412,7 @@
         <v>0.04519832</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.5298</v>
+        <v>3.0596</v>
       </c>
       <c r="Z11" t="n">
         <v>390</v>
@@ -3421,10 +3421,10 @@
         <v>1236</v>
       </c>
       <c r="AB11" t="n">
-        <v>498.5757</v>
+        <v>498.9899</v>
       </c>
       <c r="AC11" t="n">
-        <v>1479.7443</v>
+        <v>1480.1585</v>
       </c>
       <c r="AD11" t="n">
         <v>12</v>
@@ -3436,7 +3436,7 @@
         <v>20</v>
       </c>
       <c r="AG11" t="n">
-        <v>7.5279</v>
+        <v>7.5926</v>
       </c>
     </row>
     <row r="12">
@@ -3474,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
         <v>223</v>
@@ -3483,13 +3483,13 @@
         <v>629</v>
       </c>
       <c r="O12" t="n">
-        <v>16.4853</v>
+        <v>1174.1636</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="Q12" t="n">
-        <v>16.4853</v>
+        <v>33.5475</v>
       </c>
       <c r="R12" t="n">
         <v>263.4802</v>
@@ -3513,7 +3513,7 @@
         <v>0.02752735</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.3795</v>
+        <v>1.5181</v>
       </c>
       <c r="Z12" t="n">
         <v>124</v>
@@ -3575,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
         <v>99</v>
@@ -3584,13 +3584,13 @@
         <v>291</v>
       </c>
       <c r="O13" t="n">
-        <v>782.2102</v>
+        <v>898.5361</v>
       </c>
       <c r="P13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q13" t="n">
-        <v>26.0737</v>
+        <v>28.0793</v>
       </c>
       <c r="R13" t="n">
         <v>108.7696</v>
@@ -3614,7 +3614,7 @@
         <v>0.02657777</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.8387</v>
+        <v>2.7581</v>
       </c>
       <c r="Z13" t="n">
         <v>72</v>

--- a/results/542_z18/5_quantification/542_z18_quantification.xlsx
+++ b/results/542_z18/5_quantification/542_z18_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8.3636</v>
+        <v>10.3636</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>5.0452</v>
+        <v>5.0847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>400.5455</v>
+        <v>452.7273</v>
       </c>
       <c r="D13" t="n">
-        <v>403</v>
+        <v>492</v>
       </c>
       <c r="E13" t="n">
-        <v>155.5618</v>
+        <v>162.0889</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1056.4545</v>
+        <v>1131.8182</v>
       </c>
       <c r="D14" t="n">
-        <v>1100</v>
+        <v>1196</v>
       </c>
       <c r="E14" t="n">
-        <v>360.6065</v>
+        <v>370.8794</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2428.7597</v>
+        <v>2686.3819</v>
       </c>
       <c r="D15" t="n">
-        <v>2591.8368</v>
+        <v>2973.5668</v>
       </c>
       <c r="E15" t="n">
-        <v>1179.0644</v>
+        <v>986.6909000000001</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>106.3636</v>
+        <v>118.2727</v>
       </c>
       <c r="D16" t="n">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="E16" t="n">
-        <v>56.5337</v>
+        <v>46.7185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.5953</v>
+        <v>23.8444</v>
       </c>
       <c r="D17" t="n">
-        <v>22.9604</v>
+        <v>22.8151</v>
       </c>
       <c r="E17" t="n">
-        <v>4.7993</v>
+        <v>4.2105</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.03283017</v>
+        <v>0.0370072</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03212365</v>
+        <v>0.03826047</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00712545</v>
+        <v>0.00697851</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.03660992</v>
+        <v>0.03902158</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03681193</v>
+        <v>0.03818807</v>
       </c>
       <c r="E24" t="n">
-        <v>0.008027889999999999</v>
+        <v>0.00749029</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.3523</v>
+        <v>2.9114</v>
       </c>
       <c r="D25" t="n">
-        <v>2.1517</v>
+        <v>2.7581</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8814</v>
+        <v>0.8862</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>319.5455</v>
+        <v>388.6364</v>
       </c>
       <c r="D26" t="n">
-        <v>301</v>
+        <v>397</v>
       </c>
       <c r="E26" t="n">
-        <v>163.1394</v>
+        <v>163.208</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>799.1818</v>
+        <v>924.4545000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>794</v>
+        <v>961</v>
       </c>
       <c r="E27" t="n">
-        <v>378.3043</v>
+        <v>379.2185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>446.3275</v>
+        <v>507.2729</v>
       </c>
       <c r="D28" t="n">
-        <v>443.9777</v>
+        <v>547.4752</v>
       </c>
       <c r="E28" t="n">
-        <v>177.6887</v>
+        <v>185.7864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1190.8061</v>
+        <v>1278.6951</v>
       </c>
       <c r="D29" t="n">
-        <v>1240.1758</v>
+        <v>1344.8742</v>
       </c>
       <c r="E29" t="n">
-        <v>412.4413</v>
+        <v>424.9054</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9.545500000000001</v>
+        <v>11.1818</v>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E30" t="n">
-        <v>5.2605</v>
+        <v>4.8748</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>14.1818</v>
+        <v>15.0909</v>
       </c>
       <c r="D31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E31" t="n">
-        <v>6.29</v>
+        <v>6.0408</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>15.8182</v>
+        <v>16.1818</v>
       </c>
       <c r="D32" t="n">
         <v>17</v>
       </c>
       <c r="E32" t="n">
-        <v>5.3818</v>
+        <v>5.3445</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.4383</v>
+        <v>7.5225</v>
       </c>
       <c r="D33" t="n">
-        <v>7.4739</v>
+        <v>7.4427</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6045</v>
+        <v>0.593</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36688</v>
+        <v>38252</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03642689</v>
+        <v>0.03797976</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>776</v>
+        <v>828</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00077048</v>
+        <v>0.00082211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>149.1382</v>
+        <v>158.722</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.04115446</v>
+        <v>0.04293196</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03635898</v>
+        <v>0.03794367</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03642689</v>
+        <v>0.03797976</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03679624</v>
+        <v>0.03834911</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.1313</v>
+        <v>8.220700000000001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35196</v>
+        <v>36730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>596</v>
+        <v>670</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.9797</v>
+        <v>19.417</v>
       </c>
     </row>
     <row r="10">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.4438</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="11">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>43.9513</v>
+        <v>40.3731</v>
       </c>
     </row>
     <row r="12">
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.3876</v>
+        <v>0.3582</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.6418</v>
       </c>
     </row>
     <row r="15">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -2467,19 +2467,19 @@
         <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="N2" t="n">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="O2" t="n">
-        <v>1129.2641</v>
+        <v>1137.8499</v>
       </c>
       <c r="P2" t="n">
         <v>65</v>
       </c>
       <c r="Q2" t="n">
-        <v>17.3733</v>
+        <v>17.5054</v>
       </c>
       <c r="R2" t="n">
         <v>142.8112</v>
@@ -2497,25 +2497,25 @@
         <v>0.6207</v>
       </c>
       <c r="W2" t="n">
-        <v>0.04786885</v>
+        <v>0.04939891</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05016751</v>
+        <v>0.05076883</v>
       </c>
       <c r="Y2" t="n">
         <v>2.1007</v>
       </c>
       <c r="Z2" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="AA2" t="n">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="AB2" t="n">
-        <v>249.8234</v>
+        <v>256.9949</v>
       </c>
       <c r="AC2" t="n">
-        <v>658.1442</v>
+        <v>665.3158</v>
       </c>
       <c r="AD2" t="n">
         <v>4</v>
@@ -2527,7 +2527,7 @@
         <v>6</v>
       </c>
       <c r="AG2" t="n">
-        <v>7.3357</v>
+        <v>7.3669</v>
       </c>
     </row>
     <row r="3">
@@ -2568,19 +2568,19 @@
         <v>20</v>
       </c>
       <c r="M3" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="N3" t="n">
-        <v>1477</v>
+        <v>1528</v>
       </c>
       <c r="O3" t="n">
-        <v>3155.2064</v>
+        <v>2986.3952</v>
       </c>
       <c r="P3" t="n">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="Q3" t="n">
-        <v>19.72</v>
+        <v>19.7775</v>
       </c>
       <c r="R3" t="n">
         <v>625.725</v>
@@ -2598,25 +2598,25 @@
         <v>0.8861</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0405694</v>
+        <v>0.04074733</v>
       </c>
       <c r="X3" t="n">
-        <v>0.04168784</v>
+        <v>0.04312729</v>
       </c>
       <c r="Y3" t="n">
         <v>3.1963</v>
       </c>
       <c r="Z3" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="AA3" t="n">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="AB3" t="n">
-        <v>774.0975</v>
+        <v>777.0975</v>
       </c>
       <c r="AC3" t="n">
-        <v>1686.3911</v>
+        <v>1741.119</v>
       </c>
       <c r="AD3" t="n">
         <v>22</v>
@@ -2628,7 +2628,7 @@
         <v>23</v>
       </c>
       <c r="AG3" t="n">
-        <v>7.4739</v>
+        <v>7.3988</v>
       </c>
     </row>
     <row r="4">
@@ -2666,22 +2666,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M4" t="n">
-        <v>403</v>
+        <v>471</v>
       </c>
       <c r="N4" t="n">
-        <v>1085</v>
+        <v>1199</v>
       </c>
       <c r="O4" t="n">
-        <v>778.2864</v>
+        <v>3353.8216</v>
       </c>
       <c r="P4" t="n">
-        <v>24</v>
+        <v>147</v>
       </c>
       <c r="Q4" t="n">
-        <v>32.4286</v>
+        <v>22.8151</v>
       </c>
       <c r="R4" t="n">
         <v>377.0193</v>
@@ -2699,37 +2699,37 @@
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03064173</v>
+        <v>0.03581204</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03398484</v>
+        <v>0.0375556</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.061</v>
+        <v>2.1219</v>
       </c>
       <c r="Z4" t="n">
-        <v>238</v>
+        <v>397</v>
       </c>
       <c r="AA4" t="n">
-        <v>756</v>
+        <v>925</v>
       </c>
       <c r="AB4" t="n">
-        <v>443.9777</v>
+        <v>527.5462</v>
       </c>
       <c r="AC4" t="n">
-        <v>1207.6488</v>
+        <v>1344.8742</v>
       </c>
       <c r="AD4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG4" t="n">
-        <v>7.5955</v>
+        <v>7.9167</v>
       </c>
     </row>
     <row r="5">
@@ -2767,22 +2767,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M5" t="n">
-        <v>488</v>
+        <v>541</v>
       </c>
       <c r="N5" t="n">
-        <v>1259</v>
+        <v>1312</v>
       </c>
       <c r="O5" t="n">
-        <v>3608.8704</v>
+        <v>3609.2136</v>
       </c>
       <c r="P5" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.9864</v>
+        <v>22.5576</v>
       </c>
       <c r="R5" t="n">
         <v>337.7056</v>
@@ -2800,37 +2800,37 @@
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04027067</v>
+        <v>0.04464433</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04265772</v>
+        <v>0.04445348</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.1456</v>
+        <v>5.034</v>
       </c>
       <c r="Z5" t="n">
-        <v>365</v>
+        <v>450</v>
       </c>
       <c r="AA5" t="n">
-        <v>853</v>
+        <v>971</v>
       </c>
       <c r="AB5" t="n">
-        <v>541.4041</v>
+        <v>600.2030999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>1440.3545</v>
+        <v>1499.1535</v>
       </c>
       <c r="AD5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF5" t="n">
         <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>7.4471</v>
+        <v>7.3242</v>
       </c>
     </row>
     <row r="6">
@@ -2868,22 +2868,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M6" t="n">
-        <v>424</v>
+        <v>505</v>
       </c>
       <c r="N6" t="n">
-        <v>1100</v>
+        <v>1180</v>
       </c>
       <c r="O6" t="n">
-        <v>2973.7434</v>
+        <v>2370.5992</v>
       </c>
       <c r="P6" t="n">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="Q6" t="n">
-        <v>19.5641</v>
+        <v>18.6661</v>
       </c>
       <c r="R6" t="n">
         <v>371.8061</v>
@@ -2901,37 +2901,37 @@
         <v>0.9956</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03212365</v>
+        <v>0.03826047</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03451305</v>
+        <v>0.03702309</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.1517</v>
+        <v>2.9585</v>
       </c>
       <c r="Z6" t="n">
-        <v>301</v>
+        <v>351</v>
       </c>
       <c r="AA6" t="n">
-        <v>863</v>
+        <v>955</v>
       </c>
       <c r="AB6" t="n">
-        <v>470.1198</v>
+        <v>563.8894</v>
       </c>
       <c r="AC6" t="n">
-        <v>1240.1758</v>
+        <v>1334.188</v>
       </c>
       <c r="AD6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF6" t="n">
         <v>17</v>
       </c>
       <c r="AG6" t="n">
-        <v>8.1648</v>
+        <v>8.3498</v>
       </c>
     </row>
     <row r="7">
@@ -2969,22 +2969,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M7" t="n">
-        <v>385</v>
+        <v>440</v>
       </c>
       <c r="N7" t="n">
-        <v>1117</v>
+        <v>1196</v>
       </c>
       <c r="O7" t="n">
-        <v>3650.711</v>
+        <v>3371.9171</v>
       </c>
       <c r="P7" t="n">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="Q7" t="n">
-        <v>22.9604</v>
+        <v>23.5798</v>
       </c>
       <c r="R7" t="n">
         <v>308.5929</v>
@@ -3002,28 +3002,28 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03383426</v>
+        <v>0.03866772</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03935177</v>
+        <v>0.04213493</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.9443</v>
+        <v>3.2405</v>
       </c>
       <c r="Z7" t="n">
-        <v>294</v>
+        <v>366</v>
       </c>
       <c r="AA7" t="n">
-        <v>794</v>
+        <v>961</v>
       </c>
       <c r="AB7" t="n">
-        <v>429.3625</v>
+        <v>495.4041</v>
       </c>
       <c r="AC7" t="n">
-        <v>1277.9575</v>
+        <v>1371.3128</v>
       </c>
       <c r="AD7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE7" t="n">
         <v>14</v>
@@ -3032,7 +3032,7 @@
         <v>16</v>
       </c>
       <c r="AG7" t="n">
-        <v>7.1407</v>
+        <v>7.5592</v>
       </c>
     </row>
     <row r="8">
@@ -3070,22 +3070,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M8" t="n">
-        <v>552</v>
+        <v>605</v>
       </c>
       <c r="N8" t="n">
-        <v>1499</v>
+        <v>1554</v>
       </c>
       <c r="O8" t="n">
-        <v>2365.9962</v>
+        <v>2589.9201</v>
       </c>
       <c r="P8" t="n">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="Q8" t="n">
-        <v>22.1121</v>
+        <v>20.2338</v>
       </c>
       <c r="R8" t="n">
         <v>382.8772</v>
@@ -3103,28 +3103,28 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.04326019</v>
+        <v>0.04741379</v>
       </c>
       <c r="X8" t="n">
-        <v>0.04956191</v>
+        <v>0.05138039</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.3506</v>
+        <v>3.3953</v>
       </c>
       <c r="Z8" t="n">
-        <v>488</v>
+        <v>581</v>
       </c>
       <c r="AA8" t="n">
-        <v>1330</v>
+        <v>1493</v>
       </c>
       <c r="AB8" t="n">
-        <v>621.0732</v>
+        <v>684.3574</v>
       </c>
       <c r="AC8" t="n">
-        <v>1680.6266</v>
+        <v>1745.9108</v>
       </c>
       <c r="AD8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE8" t="n">
         <v>24</v>
@@ -3133,7 +3133,7 @@
         <v>20</v>
       </c>
       <c r="AG8" t="n">
-        <v>8.4041</v>
+        <v>8.382</v>
       </c>
     </row>
     <row r="9">
@@ -3171,22 +3171,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M9" t="n">
-        <v>335</v>
+        <v>371</v>
       </c>
       <c r="N9" t="n">
-        <v>963</v>
+        <v>999</v>
       </c>
       <c r="O9" t="n">
-        <v>2591.8368</v>
+        <v>2147.4032</v>
       </c>
       <c r="P9" t="n">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="Q9" t="n">
-        <v>22.3434</v>
+        <v>24.9698</v>
       </c>
       <c r="R9" t="n">
         <v>306.4924</v>
@@ -3204,28 +3204,28 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03131719</v>
+        <v>0.03468262</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03681193</v>
+        <v>0.03818807</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.6314</v>
+        <v>2.6102</v>
       </c>
       <c r="Z9" t="n">
-        <v>250</v>
+        <v>318</v>
       </c>
       <c r="AA9" t="n">
-        <v>677</v>
+        <v>862</v>
       </c>
       <c r="AB9" t="n">
-        <v>365.6934</v>
+        <v>408.2498</v>
       </c>
       <c r="AC9" t="n">
-        <v>1071.6661</v>
+        <v>1114.2224</v>
       </c>
       <c r="AD9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
         <v>13</v>
@@ -3234,7 +3234,7 @@
         <v>15</v>
       </c>
       <c r="AG9" t="n">
-        <v>7.7095</v>
+        <v>7.7776</v>
       </c>
     </row>
     <row r="10">
@@ -3272,22 +3272,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M10" t="n">
-        <v>365</v>
+        <v>512</v>
       </c>
       <c r="N10" t="n">
-        <v>878</v>
+        <v>1161</v>
       </c>
       <c r="O10" t="n">
-        <v>1474.5139</v>
+        <v>2973.5668</v>
       </c>
       <c r="P10" t="n">
-        <v>69</v>
+        <v>131</v>
       </c>
       <c r="Q10" t="n">
-        <v>21.3698</v>
+        <v>22.699</v>
       </c>
       <c r="R10" t="n">
         <v>437.262</v>
@@ -3305,37 +3305,37 @@
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02452957</v>
+        <v>0.0344086</v>
       </c>
       <c r="X10" t="n">
-        <v>0.02483664</v>
+        <v>0.03284207</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.0583</v>
+        <v>2.7444</v>
       </c>
       <c r="Z10" t="n">
-        <v>329</v>
+        <v>462</v>
       </c>
       <c r="AA10" t="n">
-        <v>651</v>
+        <v>961</v>
       </c>
       <c r="AB10" t="n">
-        <v>415.463</v>
+        <v>587.8011</v>
       </c>
       <c r="AC10" t="n">
-        <v>998.9087</v>
+        <v>1332.6854</v>
       </c>
       <c r="AD10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AF10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AG10" t="n">
-        <v>6.5411</v>
+        <v>6.8416</v>
       </c>
     </row>
     <row r="11">
@@ -3373,22 +3373,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M11" t="n">
-        <v>448</v>
+        <v>492</v>
       </c>
       <c r="N11" t="n">
-        <v>1323</v>
+        <v>1367</v>
       </c>
       <c r="O11" t="n">
-        <v>4044.4928</v>
+        <v>4072.2501</v>
       </c>
       <c r="P11" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q11" t="n">
-        <v>25.4371</v>
+        <v>25.2935</v>
       </c>
       <c r="R11" t="n">
         <v>326.8356</v>
@@ -3406,37 +3406,37 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.03784743</v>
+        <v>0.04156459</v>
       </c>
       <c r="X11" t="n">
-        <v>0.04519832</v>
+        <v>0.04670151</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.0596</v>
+        <v>2.4477</v>
       </c>
       <c r="Z11" t="n">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="AA11" t="n">
-        <v>1236</v>
+        <v>1280</v>
       </c>
       <c r="AB11" t="n">
-        <v>498.9899</v>
+        <v>547.4752</v>
       </c>
       <c r="AC11" t="n">
-        <v>1480.1585</v>
+        <v>1528.6438</v>
       </c>
       <c r="AD11" t="n">
         <v>12</v>
       </c>
       <c r="AE11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF11" t="n">
         <v>20</v>
       </c>
       <c r="AG11" t="n">
-        <v>7.5926</v>
+        <v>7.4427</v>
       </c>
     </row>
     <row r="12">
@@ -3477,19 +3477,19 @@
         <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="N12" t="n">
-        <v>629</v>
+        <v>658</v>
       </c>
       <c r="O12" t="n">
-        <v>1174.1636</v>
+        <v>1176.5778</v>
       </c>
       <c r="P12" t="n">
         <v>35</v>
       </c>
       <c r="Q12" t="n">
-        <v>33.5475</v>
+        <v>33.6165</v>
       </c>
       <c r="R12" t="n">
         <v>263.4802</v>
@@ -3507,37 +3507,37 @@
         <v>0.8783</v>
       </c>
       <c r="W12" t="n">
-        <v>0.02237159</v>
+        <v>0.0252809</v>
       </c>
       <c r="X12" t="n">
-        <v>0.02752735</v>
+        <v>0.0287965</v>
       </c>
       <c r="Y12" t="n">
         <v>1.5181</v>
       </c>
       <c r="Z12" t="n">
-        <v>124</v>
+        <v>167</v>
       </c>
       <c r="AA12" t="n">
-        <v>231</v>
+        <v>303</v>
       </c>
       <c r="AB12" t="n">
-        <v>245.7229</v>
+        <v>278.865</v>
       </c>
       <c r="AC12" t="n">
-        <v>700.328</v>
+        <v>733.4701</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF12" t="n">
         <v>8</v>
       </c>
       <c r="AG12" t="n">
-        <v>7.398</v>
+        <v>7.3845</v>
       </c>
     </row>
     <row r="13">
@@ -3578,10 +3578,10 @@
         <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="N13" t="n">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="O13" t="n">
         <v>898.5361</v>
@@ -3608,28 +3608,28 @@
         <v>0.75</v>
       </c>
       <c r="W13" t="n">
-        <v>0.02436623</v>
+        <v>0.02559685</v>
       </c>
       <c r="X13" t="n">
-        <v>0.02657777</v>
+        <v>0.02703443</v>
       </c>
       <c r="Y13" t="n">
         <v>2.7581</v>
       </c>
       <c r="Z13" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AA13" t="n">
-        <v>166</v>
+        <v>221</v>
       </c>
       <c r="AB13" t="n">
-        <v>103.6985</v>
+        <v>109.1127</v>
       </c>
       <c r="AC13" t="n">
-        <v>314.6518</v>
+        <v>320.066</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
@@ -3638,7 +3638,7 @@
         <v>5</v>
       </c>
       <c r="AG13" t="n">
-        <v>6.3545</v>
+        <v>6.3702</v>
       </c>
     </row>
     <row r="14">

--- a/results/542_z18/5_quantification/542_z18_quantification.xlsx
+++ b/results/542_z18/5_quantification/542_z18_quantification.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10.3636</v>
+        <v>11.8182</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>5.0847</v>
+        <v>6.3532</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>452.7273</v>
+        <v>478.0909</v>
       </c>
       <c r="D13" t="n">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="E13" t="n">
-        <v>162.0889</v>
+        <v>170.2066</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1131.8182</v>
+        <v>1163.5455</v>
       </c>
       <c r="D14" t="n">
-        <v>1196</v>
+        <v>1225</v>
       </c>
       <c r="E14" t="n">
-        <v>370.8794</v>
+        <v>379.8485</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2686.3819</v>
+        <v>2866.3524</v>
       </c>
       <c r="D15" t="n">
-        <v>2973.5668</v>
+        <v>3328.4734</v>
       </c>
       <c r="E15" t="n">
-        <v>986.6909000000001</v>
+        <v>977.3682</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>118.2727</v>
+        <v>129.8182</v>
       </c>
       <c r="D16" t="n">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="E16" t="n">
-        <v>46.7185</v>
+        <v>48.4826</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.8444</v>
+        <v>23.2149</v>
       </c>
       <c r="D17" t="n">
-        <v>22.8151</v>
+        <v>22.1254</v>
       </c>
       <c r="E17" t="n">
-        <v>4.2105</v>
+        <v>4.4646</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0370072</v>
+        <v>0.03936536</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03826047</v>
+        <v>0.04066561</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00697851</v>
+        <v>0.00724071</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.03902158</v>
+        <v>0.04019659</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03818807</v>
+        <v>0.04078746</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00749029</v>
+        <v>0.0076868</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.9114</v>
+        <v>3.316</v>
       </c>
       <c r="D25" t="n">
-        <v>2.7581</v>
+        <v>3.2017</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8862</v>
+        <v>0.9923</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>388.6364</v>
+        <v>429.6364</v>
       </c>
       <c r="D26" t="n">
-        <v>397</v>
+        <v>449</v>
       </c>
       <c r="E26" t="n">
-        <v>163.208</v>
+        <v>178.4451</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>924.4545000000001</v>
+        <v>987.3636</v>
       </c>
       <c r="D27" t="n">
-        <v>961</v>
+        <v>1012</v>
       </c>
       <c r="E27" t="n">
-        <v>379.2185</v>
+        <v>390.0757</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>507.2729</v>
+        <v>536.5021</v>
       </c>
       <c r="D28" t="n">
-        <v>547.4752</v>
+        <v>556.0315000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>185.7864</v>
+        <v>195.9253</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1278.6951</v>
+        <v>1315.11</v>
       </c>
       <c r="D29" t="n">
-        <v>1344.8742</v>
+        <v>1372.9453</v>
       </c>
       <c r="E29" t="n">
-        <v>424.9054</v>
+        <v>434.9466</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>11.1818</v>
+        <v>11.9091</v>
       </c>
       <c r="D30" t="n">
         <v>12</v>
       </c>
       <c r="E30" t="n">
-        <v>4.8748</v>
+        <v>4.9891</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>15.0909</v>
+        <v>15.2727</v>
       </c>
       <c r="D31" t="n">
         <v>15</v>
       </c>
       <c r="E31" t="n">
-        <v>6.0408</v>
+        <v>5.8837</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>16.1818</v>
+        <v>16.4545</v>
       </c>
       <c r="D32" t="n">
         <v>17</v>
       </c>
       <c r="E32" t="n">
-        <v>5.3445</v>
+        <v>5.336</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1299,29 +1299,87 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>loop_count</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>loops, report only</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>10.8182</v>
+      </c>
+      <c r="D33" t="n">
+        <v>12</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6.0633</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>loop_edge_share</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>loops, report only</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.0951</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>ring_width_mean_r30_px</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>width</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>7.5225</v>
-      </c>
-      <c r="D33" t="n">
-        <v>7.4427</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="C35" t="n">
+        <v>7.6437</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7.7704</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.4379</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>px</t>
         </is>
       </c>
-      <c r="G33" t="n">
+      <c r="G35" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1336,7 +1394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1393,7 +1451,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38252</v>
+        <v>39183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1471,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03797976</v>
+        <v>0.03890414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1491,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>828</v>
+        <v>886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1511,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00082211</v>
+        <v>0.00087969</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1513,7 +1571,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1591,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>158.722</v>
+        <v>168.8922</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1611,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1631,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.04293196</v>
+        <v>0.04398086</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1651,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03794367</v>
+        <v>0.03883208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1728,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03797976</v>
+        <v>0.03890414</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,11 +1748,71 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03834911</v>
+        <v>0.03927349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>loop_count</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>156</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>loop_edge_share</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>edge_count</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1936</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>count</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1864,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.220700000000001</v>
+        <v>8.241099999999999</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1826,7 +1944,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36730</v>
+        <v>37590</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +2087,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>670</v>
+        <v>718</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +2102,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.417</v>
+        <v>19.1439</v>
       </c>
     </row>
     <row r="10">
@@ -2014,7 +2132,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>40.3731</v>
+        <v>41.5891</v>
       </c>
     </row>
     <row r="12">
@@ -2029,7 +2147,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>50.0379</v>
+        <v>50.0471</v>
       </c>
     </row>
     <row r="13">
@@ -2044,7 +2162,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.3582</v>
+        <v>0.3565</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2177,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6418</v>
+        <v>0.6435</v>
       </c>
     </row>
     <row r="15">
@@ -2136,7 +2254,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -2151,7 +2269,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
@@ -2259,7 +2377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG14"/>
+  <dimension ref="A1:AI14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2428,6 +2546,16 @@
           <t>ring_width_mean_r30_px</t>
         </is>
       </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>loop_count</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>loop_edge_share</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2467,19 +2595,19 @@
         <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="N2" t="n">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="O2" t="n">
-        <v>1137.8499</v>
+        <v>1147.1636</v>
       </c>
       <c r="P2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="Q2" t="n">
-        <v>17.5054</v>
+        <v>16.8701</v>
       </c>
       <c r="R2" t="n">
         <v>142.8112</v>
@@ -2497,28 +2625,28 @@
         <v>0.6207</v>
       </c>
       <c r="W2" t="n">
-        <v>0.04939891</v>
+        <v>0.04874317</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05076883</v>
+        <v>0.05051112</v>
       </c>
       <c r="Y2" t="n">
         <v>2.1007</v>
       </c>
       <c r="Z2" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA2" t="n">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AB2" t="n">
-        <v>256.9949</v>
+        <v>255.8944</v>
       </c>
       <c r="AC2" t="n">
-        <v>665.3158</v>
+        <v>664.2153</v>
       </c>
       <c r="AD2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -2527,7 +2655,13 @@
         <v>6</v>
       </c>
       <c r="AG2" t="n">
-        <v>7.3669</v>
+        <v>7.2808</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.2206</v>
       </c>
     </row>
     <row r="3">
@@ -2565,22 +2699,22 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M3" t="n">
-        <v>687</v>
+        <v>754</v>
       </c>
       <c r="N3" t="n">
-        <v>1528</v>
+        <v>1600</v>
       </c>
       <c r="O3" t="n">
-        <v>2986.3952</v>
+        <v>3117.6917</v>
       </c>
       <c r="P3" t="n">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="Q3" t="n">
-        <v>19.7775</v>
+        <v>19.0103</v>
       </c>
       <c r="R3" t="n">
         <v>625.725</v>
@@ -2598,28 +2732,28 @@
         <v>0.8861</v>
       </c>
       <c r="W3" t="n">
-        <v>0.04074733</v>
+        <v>0.04472123</v>
       </c>
       <c r="X3" t="n">
-        <v>0.04312729</v>
+        <v>0.04515947</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.1963</v>
+        <v>4.1552</v>
       </c>
       <c r="Z3" t="n">
-        <v>667</v>
+        <v>734</v>
       </c>
       <c r="AA3" t="n">
-        <v>1237</v>
+        <v>1304</v>
       </c>
       <c r="AB3" t="n">
-        <v>777.0975</v>
+        <v>857.1097</v>
       </c>
       <c r="AC3" t="n">
-        <v>1741.119</v>
+        <v>1827.9596</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
         <v>24</v>
@@ -2628,7 +2762,13 @@
         <v>23</v>
       </c>
       <c r="AG3" t="n">
-        <v>7.3988</v>
+        <v>7.4838</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.3049</v>
       </c>
     </row>
     <row r="4">
@@ -2666,22 +2806,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
-        <v>471</v>
+        <v>497</v>
       </c>
       <c r="N4" t="n">
-        <v>1199</v>
+        <v>1225</v>
       </c>
       <c r="O4" t="n">
-        <v>3353.8216</v>
+        <v>3407.3069</v>
       </c>
       <c r="P4" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="Q4" t="n">
-        <v>22.8151</v>
+        <v>22.1254</v>
       </c>
       <c r="R4" t="n">
         <v>377.0193</v>
@@ -2699,37 +2839,43 @@
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03581204</v>
+        <v>0.03778893</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0375556</v>
+        <v>0.03836998</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.1219</v>
+        <v>2.6524</v>
       </c>
       <c r="Z4" t="n">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="AA4" t="n">
-        <v>925</v>
+        <v>943</v>
       </c>
       <c r="AB4" t="n">
-        <v>527.5462</v>
+        <v>556.0315000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>1344.8742</v>
+        <v>1372.9453</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AF4" t="n">
         <v>19</v>
       </c>
       <c r="AG4" t="n">
-        <v>7.9167</v>
+        <v>7.9316</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.2792</v>
       </c>
     </row>
     <row r="5">
@@ -2767,22 +2913,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M5" t="n">
-        <v>541</v>
+        <v>574</v>
       </c>
       <c r="N5" t="n">
-        <v>1312</v>
+        <v>1352</v>
       </c>
       <c r="O5" t="n">
-        <v>3609.2136</v>
+        <v>3709.8115</v>
       </c>
       <c r="P5" t="n">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.5576</v>
+        <v>21.6948</v>
       </c>
       <c r="R5" t="n">
         <v>337.7056</v>
@@ -2800,28 +2946,28 @@
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04464433</v>
+        <v>0.04736755</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04445348</v>
+        <v>0.04580877</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.034</v>
+        <v>5.6262</v>
       </c>
       <c r="Z5" t="n">
-        <v>450</v>
+        <v>545</v>
       </c>
       <c r="AA5" t="n">
-        <v>971</v>
+        <v>1144</v>
       </c>
       <c r="AB5" t="n">
-        <v>600.2030999999999</v>
+        <v>644.9016</v>
       </c>
       <c r="AC5" t="n">
-        <v>1499.1535</v>
+        <v>1549.8519</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -2830,7 +2976,13 @@
         <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>7.3242</v>
+        <v>7.3871</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.3333</v>
       </c>
     </row>
     <row r="6">
@@ -2868,22 +3020,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>505</v>
+        <v>451</v>
       </c>
       <c r="N6" t="n">
-        <v>1180</v>
+        <v>1129</v>
       </c>
       <c r="O6" t="n">
-        <v>2370.5992</v>
+        <v>2308.4865</v>
       </c>
       <c r="P6" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.6661</v>
+        <v>18.6168</v>
       </c>
       <c r="R6" t="n">
         <v>371.8061</v>
@@ -2901,37 +3053,43 @@
         <v>0.9956</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03826047</v>
+        <v>0.03416926</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03702309</v>
+        <v>0.03542294</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.9585</v>
+        <v>2.6896</v>
       </c>
       <c r="Z6" t="n">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="AA6" t="n">
-        <v>955</v>
+        <v>942</v>
       </c>
       <c r="AB6" t="n">
-        <v>563.8894</v>
+        <v>498.7767</v>
       </c>
       <c r="AC6" t="n">
-        <v>1334.188</v>
+        <v>1272.661</v>
       </c>
       <c r="AD6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AF6" t="n">
         <v>17</v>
       </c>
       <c r="AG6" t="n">
-        <v>8.3498</v>
+        <v>8.109299999999999</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.4919</v>
       </c>
     </row>
     <row r="7">
@@ -2972,19 +3130,19 @@
         <v>10</v>
       </c>
       <c r="M7" t="n">
-        <v>440</v>
+        <v>479</v>
       </c>
       <c r="N7" t="n">
-        <v>1196</v>
+        <v>1243</v>
       </c>
       <c r="O7" t="n">
-        <v>3371.9171</v>
+        <v>3455.3729</v>
       </c>
       <c r="P7" t="n">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="Q7" t="n">
-        <v>23.5798</v>
+        <v>22.5841</v>
       </c>
       <c r="R7" t="n">
         <v>308.5929</v>
@@ -3002,37 +3160,43 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03866772</v>
+        <v>0.04209509</v>
       </c>
       <c r="X7" t="n">
-        <v>0.04213493</v>
+        <v>0.04379073</v>
       </c>
       <c r="Y7" t="n">
         <v>3.2405</v>
       </c>
       <c r="Z7" t="n">
-        <v>366</v>
+        <v>449</v>
       </c>
       <c r="AA7" t="n">
-        <v>961</v>
+        <v>1104</v>
       </c>
       <c r="AB7" t="n">
-        <v>495.4041</v>
+        <v>540.3747</v>
       </c>
       <c r="AC7" t="n">
-        <v>1371.3128</v>
+        <v>1422.455</v>
       </c>
       <c r="AD7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG7" t="n">
-        <v>7.5592</v>
+        <v>8.0328</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.3399</v>
       </c>
     </row>
     <row r="8">
@@ -3070,22 +3234,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M8" t="n">
-        <v>605</v>
+        <v>637</v>
       </c>
       <c r="N8" t="n">
-        <v>1554</v>
+        <v>1592</v>
       </c>
       <c r="O8" t="n">
-        <v>2589.9201</v>
+        <v>2223.4276</v>
       </c>
       <c r="P8" t="n">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="Q8" t="n">
-        <v>20.2338</v>
+        <v>20.0309</v>
       </c>
       <c r="R8" t="n">
         <v>382.8772</v>
@@ -3103,37 +3267,43 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.04741379</v>
+        <v>0.04992163</v>
       </c>
       <c r="X8" t="n">
-        <v>0.05138039</v>
+        <v>0.0526368</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.3953</v>
+        <v>3.9177</v>
       </c>
       <c r="Z8" t="n">
-        <v>581</v>
+        <v>612</v>
       </c>
       <c r="AA8" t="n">
-        <v>1493</v>
+        <v>1526</v>
       </c>
       <c r="AB8" t="n">
-        <v>684.3574</v>
+        <v>713.529</v>
       </c>
       <c r="AC8" t="n">
-        <v>1745.9108</v>
+        <v>1782.325</v>
       </c>
       <c r="AD8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF8" t="n">
         <v>20</v>
       </c>
       <c r="AG8" t="n">
-        <v>8.382</v>
+        <v>8.176399999999999</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.1441</v>
       </c>
     </row>
     <row r="9">
@@ -3171,22 +3341,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M9" t="n">
-        <v>371</v>
+        <v>435</v>
       </c>
       <c r="N9" t="n">
-        <v>999</v>
+        <v>1067</v>
       </c>
       <c r="O9" t="n">
-        <v>2147.4032</v>
+        <v>3958.5517</v>
       </c>
       <c r="P9" t="n">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="Q9" t="n">
-        <v>24.9698</v>
+        <v>23.0148</v>
       </c>
       <c r="R9" t="n">
         <v>306.4924</v>
@@ -3204,37 +3374,43 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03468262</v>
+        <v>0.04066561</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03818807</v>
+        <v>0.04078746</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.6102</v>
+        <v>2.2839</v>
       </c>
       <c r="Z9" t="n">
-        <v>318</v>
+        <v>382</v>
       </c>
       <c r="AA9" t="n">
-        <v>862</v>
+        <v>1012</v>
       </c>
       <c r="AB9" t="n">
-        <v>408.2498</v>
+        <v>484.5341</v>
       </c>
       <c r="AC9" t="n">
-        <v>1114.2224</v>
+        <v>1196.9209</v>
       </c>
       <c r="AD9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AF9" t="n">
         <v>15</v>
       </c>
       <c r="AG9" t="n">
-        <v>7.7776</v>
+        <v>7.8014</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.407</v>
       </c>
     </row>
     <row r="10">
@@ -3272,22 +3448,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M10" t="n">
-        <v>512</v>
+        <v>530</v>
       </c>
       <c r="N10" t="n">
-        <v>1161</v>
+        <v>1195</v>
       </c>
       <c r="O10" t="n">
-        <v>2973.5668</v>
+        <v>3328.4734</v>
       </c>
       <c r="P10" t="n">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="Q10" t="n">
-        <v>22.699</v>
+        <v>22.0429</v>
       </c>
       <c r="R10" t="n">
         <v>437.262</v>
@@ -3305,37 +3481,43 @@
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0344086</v>
+        <v>0.03561828</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03284207</v>
+        <v>0.03380385</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.7444</v>
+        <v>3.2017</v>
       </c>
       <c r="Z10" t="n">
-        <v>462</v>
+        <v>498</v>
       </c>
       <c r="AA10" t="n">
-        <v>961</v>
+        <v>994</v>
       </c>
       <c r="AB10" t="n">
-        <v>587.8011</v>
+        <v>608.4579</v>
       </c>
       <c r="AC10" t="n">
-        <v>1332.6854</v>
+        <v>1362.4428</v>
       </c>
       <c r="AD10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE10" t="n">
         <v>14</v>
       </c>
-      <c r="AE10" t="n">
-        <v>13</v>
-      </c>
       <c r="AF10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG10" t="n">
-        <v>6.8416</v>
+        <v>7.2273</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.351</v>
       </c>
     </row>
     <row r="11">
@@ -3373,22 +3555,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M11" t="n">
-        <v>492</v>
+        <v>517</v>
       </c>
       <c r="N11" t="n">
-        <v>1367</v>
+        <v>1402</v>
       </c>
       <c r="O11" t="n">
-        <v>4072.2501</v>
+        <v>3590.846</v>
       </c>
       <c r="P11" t="n">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="Q11" t="n">
-        <v>25.2935</v>
+        <v>23.939</v>
       </c>
       <c r="R11" t="n">
         <v>326.8356</v>
@@ -3406,37 +3588,43 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.04156459</v>
+        <v>0.04367661</v>
       </c>
       <c r="X11" t="n">
-        <v>0.04670151</v>
+        <v>0.04789724</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.4477</v>
+        <v>2.7537</v>
       </c>
       <c r="Z11" t="n">
-        <v>420</v>
+        <v>458</v>
       </c>
       <c r="AA11" t="n">
-        <v>1280</v>
+        <v>1314</v>
       </c>
       <c r="AB11" t="n">
-        <v>547.4752</v>
+        <v>579.7595</v>
       </c>
       <c r="AC11" t="n">
-        <v>1528.6438</v>
+        <v>1576.656</v>
       </c>
       <c r="AD11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
         <v>17</v>
       </c>
       <c r="AF11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>7.4289</v>
+      </c>
+      <c r="AH11" t="n">
         <v>20</v>
       </c>
-      <c r="AG11" t="n">
-        <v>7.4427</v>
+      <c r="AI11" t="n">
+        <v>0.4667</v>
       </c>
     </row>
     <row r="12">
@@ -3474,22 +3662,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M12" t="n">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="N12" t="n">
-        <v>658</v>
+        <v>679</v>
       </c>
       <c r="O12" t="n">
-        <v>1176.5778</v>
+        <v>1333.6316</v>
       </c>
       <c r="P12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="Q12" t="n">
-        <v>33.6165</v>
+        <v>34.1957</v>
       </c>
       <c r="R12" t="n">
         <v>263.4802</v>
@@ -3507,25 +3695,25 @@
         <v>0.8783</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0252809</v>
+        <v>0.02598315</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0287965</v>
+        <v>0.02971554</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.5181</v>
+        <v>2.2772</v>
       </c>
       <c r="Z12" t="n">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="AA12" t="n">
-        <v>303</v>
+        <v>345</v>
       </c>
       <c r="AB12" t="n">
-        <v>278.865</v>
+        <v>286.2792</v>
       </c>
       <c r="AC12" t="n">
-        <v>733.4701</v>
+        <v>758.7838</v>
       </c>
       <c r="AD12" t="n">
         <v>7</v>
@@ -3537,7 +3725,13 @@
         <v>8</v>
       </c>
       <c r="AG12" t="n">
-        <v>7.3845</v>
+        <v>7.7704</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.2821</v>
       </c>
     </row>
     <row r="13">
@@ -3575,22 +3769,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M13" t="n">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="N13" t="n">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="O13" t="n">
-        <v>898.5361</v>
+        <v>1096.2763</v>
       </c>
       <c r="P13" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="Q13" t="n">
-        <v>28.0793</v>
+        <v>28.1096</v>
       </c>
       <c r="R13" t="n">
         <v>108.7696</v>
@@ -3608,25 +3802,25 @@
         <v>0.75</v>
       </c>
       <c r="W13" t="n">
-        <v>0.02559685</v>
+        <v>0.03101157</v>
       </c>
       <c r="X13" t="n">
-        <v>0.02703443</v>
+        <v>0.02876975</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.7581</v>
+        <v>3.6775</v>
       </c>
       <c r="Z13" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="AA13" t="n">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="AB13" t="n">
-        <v>109.1127</v>
+        <v>131.7696</v>
       </c>
       <c r="AC13" t="n">
-        <v>320.066</v>
+        <v>343.2082</v>
       </c>
       <c r="AD13" t="n">
         <v>3</v>
@@ -3635,10 +3829,16 @@
         <v>3</v>
       </c>
       <c r="AF13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG13" t="n">
-        <v>6.3702</v>
+        <v>6.732</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.3333</v>
       </c>
     </row>
     <row r="14">
@@ -3661,7 +3861,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -3691,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.00464157</v>
+        <v>0.0051573</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -3706,7 +3906,7 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.0711</v>
+        <v>11.4853</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -3715,6 +3915,12 @@
         <v>0</v>
       </c>
       <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
         <v>0</v>
       </c>
     </row>
